--- a/research/traditional_assets/database/data/new_zealand/new_zealand_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_oilfield_svcs_equip.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nzse_chi" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.102</v>
+        <v>-0.0767</v>
       </c>
       <c r="G2">
-        <v>0.1677934849416103</v>
+        <v>0.2966153846153846</v>
       </c>
       <c r="H2">
-        <v>0.1677934849416103</v>
+        <v>0.2966153846153846</v>
       </c>
       <c r="I2">
-        <v>-0.06072526121696375</v>
+        <v>0.001858461538461538</v>
       </c>
       <c r="J2">
-        <v>-0.06072526121696375</v>
+        <v>0.001858461538461538</v>
       </c>
       <c r="K2">
-        <v>-11.8</v>
+        <v>-330.2</v>
       </c>
       <c r="L2">
-        <v>-0.07252612169637371</v>
+        <v>-2.032</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>24.1</v>
+        <v>5.01</v>
       </c>
       <c r="V2">
-        <v>0.1009212730318258</v>
+        <v>0.01487088156723063</v>
       </c>
       <c r="W2">
-        <v>-0.03291492329149233</v>
+        <v>-0.8189484126984127</v>
       </c>
       <c r="X2">
-        <v>0.08168103230039023</v>
+        <v>0.1097958223642336</v>
       </c>
       <c r="Y2">
-        <v>-0.1145959555918826</v>
+        <v>-0.9287442350626463</v>
       </c>
       <c r="Z2">
-        <v>0.3114471669218989</v>
+        <v>0.2859908482928546</v>
       </c>
       <c r="AA2">
-        <v>-0.01891271056661562</v>
+        <v>0.0005315029919042591</v>
       </c>
       <c r="AB2">
-        <v>0.05448183290753869</v>
+        <v>0.08749421184190635</v>
       </c>
       <c r="AC2">
-        <v>-0.07339454347415431</v>
+        <v>-0.0869627088500021</v>
       </c>
       <c r="AD2">
-        <v>189.1</v>
+        <v>140.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>189.1</v>
+        <v>140.6</v>
       </c>
       <c r="AG2">
-        <v>165</v>
+        <v>135.59</v>
       </c>
       <c r="AH2">
-        <v>0.4419256835709278</v>
+        <v>0.2944502617801047</v>
       </c>
       <c r="AI2">
-        <v>0.3192638865439811</v>
+        <v>0.3019111015675327</v>
       </c>
       <c r="AJ2">
-        <v>0.4086181277860327</v>
+        <v>0.2869690363817224</v>
       </c>
       <c r="AK2">
-        <v>0.2903907074973601</v>
+        <v>0.2943193904794981</v>
       </c>
       <c r="AL2">
-        <v>6.99</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AM2">
-        <v>6.936</v>
+        <v>9.097000000000001</v>
       </c>
       <c r="AN2">
-        <v>4.049250535331906</v>
+        <v>3.927374301675978</v>
       </c>
       <c r="AO2">
-        <v>-1.413447782546495</v>
+        <v>0.03279044516829533</v>
       </c>
       <c r="AP2">
-        <v>3.533190578158458</v>
+        <v>3.787430167597766</v>
       </c>
       <c r="AQ2">
-        <v>-1.424452133794694</v>
+        <v>0.03319775750247334</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +709,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The New Zealand Refining Company Limited (NZSE:NZR)</t>
+          <t>Channel Infrastructure NZ Limited (NZSE:CHI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.102</v>
+        <v>-0.0767</v>
       </c>
       <c r="G3">
-        <v>0.1677934849416103</v>
+        <v>0.2966153846153846</v>
       </c>
       <c r="H3">
-        <v>0.1677934849416103</v>
+        <v>0.2966153846153846</v>
       </c>
       <c r="I3">
-        <v>-0.06072526121696375</v>
+        <v>0.001858461538461538</v>
       </c>
       <c r="J3">
-        <v>-0.06072526121696375</v>
+        <v>0.001858461538461538</v>
       </c>
       <c r="K3">
-        <v>-11.8</v>
+        <v>-330.2</v>
       </c>
       <c r="L3">
-        <v>-0.07252612169637371</v>
+        <v>-2.032</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8774 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>24.1</v>
+        <v>5.01</v>
       </c>
       <c r="V3">
-        <v>0.1009212730318258</v>
+        <v>0.01487088156723063</v>
       </c>
       <c r="W3">
-        <v>-0.03291492329149233</v>
+        <v>-0.8189484126984127</v>
       </c>
       <c r="X3">
-        <v>0.08168103230039023</v>
+        <v>0.1097958223642336</v>
       </c>
       <c r="Y3">
-        <v>-0.1145959555918826</v>
+        <v>-0.9287442350626463</v>
       </c>
       <c r="Z3">
-        <v>0.3114471669218989</v>
+        <v>0.2859908482928546</v>
       </c>
       <c r="AA3">
-        <v>-0.01891271056661562</v>
+        <v>0.0005315029919042591</v>
       </c>
       <c r="AB3">
-        <v>0.05448183290753869</v>
+        <v>0.08749421184190635</v>
       </c>
       <c r="AC3">
-        <v>-0.07339454347415431</v>
+        <v>-0.0869627088500021</v>
       </c>
       <c r="AD3">
-        <v>189.1</v>
+        <v>140.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>189.1</v>
+        <v>140.6</v>
       </c>
       <c r="AG3">
+        <v>135.59</v>
+      </c>
+      <c r="AH3">
+        <v>0.2944502617801047</v>
+      </c>
+      <c r="AI3">
+        <v>0.3019111015675327</v>
+      </c>
+      <c r="AJ3">
+        <v>0.2869690363817224</v>
+      </c>
+      <c r="AK3">
+        <v>0.2943193904794981</v>
+      </c>
+      <c r="AL3">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="AM3">
+        <v>9.097000000000001</v>
+      </c>
+      <c r="AN3">
+        <v>3.927374301675978</v>
+      </c>
+      <c r="AO3">
+        <v>0.03279044516829533</v>
+      </c>
+      <c r="AP3">
+        <v>3.787430167597766</v>
+      </c>
+      <c r="AQ3">
+        <v>0.03319775750247334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Channel Infrastructure NZ Limited (NZSE:CHI)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NZSE:CHI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oilfield Svcs/Equip.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.294450261780105</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>336.9</v>
+      </c>
+      <c r="H2">
+        <v>320.132654898528</v>
+      </c>
+      <c r="I2">
+        <v>472.49</v>
+      </c>
+      <c r="J2">
+        <v>319.897654898528</v>
+      </c>
+      <c r="K2">
+        <v>140.6</v>
+      </c>
+      <c r="L2">
+        <v>4.775</v>
+      </c>
+      <c r="M2">
+        <v>0.08749421184190639</v>
+      </c>
+      <c r="N2">
+        <v>0.110737376636508</v>
+      </c>
+      <c r="O2">
+        <v>0.034056</v>
+      </c>
+      <c r="P2">
+        <v>1.48780523560209</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.109795822364234</v>
+      </c>
+      <c r="T2">
+        <v>0.09682760028332001</v>
+      </c>
+      <c r="U2">
+        <v>1.20042167094706</v>
+      </c>
+      <c r="V2">
+        <v>0.981150532150796</v>
+      </c>
+      <c r="W2">
+        <v>-18.67978636638691</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>336.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.0473</v>
+      </c>
+      <c r="AD2">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>35.8</v>
+      </c>
+      <c r="AH2">
+        <v>57.1</v>
+      </c>
+      <c r="AI2">
+        <v>19.6</v>
+      </c>
+      <c r="AJ2">
+        <v>140.6</v>
+      </c>
+      <c r="AK2">
+        <v>140.6</v>
+      </c>
+      <c r="AL2">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="AM2">
+        <v>140.6</v>
+      </c>
+      <c r="AN2">
+        <v>5.01</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-140.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>5.01</v>
+      </c>
+      <c r="H2">
+        <v>336.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>35.8</v>
+      </c>
+      <c r="K2">
+        <v>57.1</v>
+      </c>
+      <c r="L2">
+        <v>-21.3</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-21.3</v>
+      </c>
+      <c r="O2">
+        <v>-5.964</v>
+      </c>
+      <c r="P2">
+        <v>-15.33600000000001</v>
+      </c>
+      <c r="Q2">
+        <v>41.764</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1107373766365077</v>
+      </c>
+      <c r="C3">
+        <v>320.1326548985276</v>
+      </c>
+      <c r="D3">
+        <v>319.8976548985275</v>
+      </c>
+      <c r="E3">
+        <v>-135.825</v>
+      </c>
+      <c r="F3">
+        <v>4.775</v>
+      </c>
+      <c r="G3">
+        <v>5.01</v>
+      </c>
+      <c r="H3">
+        <v>336.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>35.8</v>
+      </c>
+      <c r="K3">
+        <v>57.1</v>
+      </c>
+      <c r="L3">
+        <v>-21.3</v>
+      </c>
+      <c r="M3">
+        <v>1.14027</v>
+      </c>
+      <c r="N3">
+        <v>-22.44027000000001</v>
+      </c>
+      <c r="O3">
+        <v>-6.2832756</v>
+      </c>
+      <c r="P3">
+        <v>-16.15699440000001</v>
+      </c>
+      <c r="Q3">
+        <v>40.94300559999999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09682760028331999</v>
+      </c>
+      <c r="T3">
+        <v>0.9811505321507961</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-5.230340182588333</v>
+      </c>
+      <c r="W3">
+        <v>1.487805235602094</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-18.67978636638691</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1127373766365077</v>
+      </c>
+      <c r="C4">
+        <v>306.7083362136635</v>
+      </c>
+      <c r="D4">
+        <v>311.2483362136635</v>
+      </c>
+      <c r="E4">
+        <v>-131.05</v>
+      </c>
+      <c r="F4">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="G4">
+        <v>5.01</v>
+      </c>
+      <c r="H4">
+        <v>336.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>35.8</v>
+      </c>
+      <c r="K4">
+        <v>57.1</v>
+      </c>
+      <c r="L4">
+        <v>-21.3</v>
+      </c>
+      <c r="M4">
+        <v>2.28054</v>
+      </c>
+      <c r="N4">
+        <v>-23.58054000000001</v>
+      </c>
+      <c r="O4">
+        <v>-6.6025512</v>
+      </c>
+      <c r="P4">
+        <v>-16.97798880000001</v>
+      </c>
+      <c r="Q4">
+        <v>40.1220112</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09741971865355795</v>
+      </c>
+      <c r="T4">
+        <v>0.9911622722747838</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-2.615170091294166</v>
+      </c>
+      <c r="W4">
+        <v>0.863302617801047</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-9.339893183193455</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1147373766365077</v>
+      </c>
+      <c r="C5">
+        <v>293.7394209853974</v>
+      </c>
+      <c r="D5">
+        <v>303.0544209853974</v>
+      </c>
+      <c r="E5">
+        <v>-126.275</v>
+      </c>
+      <c r="F5">
+        <v>14.325</v>
+      </c>
+      <c r="G5">
+        <v>5.01</v>
+      </c>
+      <c r="H5">
+        <v>336.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>35.8</v>
+      </c>
+      <c r="K5">
+        <v>57.1</v>
+      </c>
+      <c r="L5">
+        <v>-21.3</v>
+      </c>
+      <c r="M5">
+        <v>3.42081</v>
+      </c>
+      <c r="N5">
+        <v>-24.72081</v>
+      </c>
+      <c r="O5">
+        <v>-6.921826799999999</v>
+      </c>
+      <c r="P5">
+        <v>-17.79898320000001</v>
+      </c>
+      <c r="Q5">
+        <v>39.3010168</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09802404564998637</v>
+      </c>
+      <c r="T5">
+        <v>1.001380440030194</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-1.743446727529445</v>
+      </c>
+      <c r="W5">
+        <v>0.6551350785340313</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-6.226595455462304</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1167373766365077</v>
+      </c>
+      <c r="C6">
+        <v>281.1908649705098</v>
+      </c>
+      <c r="D6">
+        <v>295.2808649705098</v>
+      </c>
+      <c r="E6">
+        <v>-121.5</v>
+      </c>
+      <c r="F6">
+        <v>19.1</v>
+      </c>
+      <c r="G6">
+        <v>5.01</v>
+      </c>
+      <c r="H6">
+        <v>336.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>35.8</v>
+      </c>
+      <c r="K6">
+        <v>57.1</v>
+      </c>
+      <c r="L6">
+        <v>-21.3</v>
+      </c>
+      <c r="M6">
+        <v>4.56108</v>
+      </c>
+      <c r="N6">
+        <v>-25.86108</v>
+      </c>
+      <c r="O6">
+        <v>-7.241102399999999</v>
+      </c>
+      <c r="P6">
+        <v>-18.61997760000001</v>
+      </c>
+      <c r="Q6">
+        <v>38.4800224</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09864096279217374</v>
+      </c>
+      <c r="T6">
+        <v>1.011811486280509</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-1.307585045647083</v>
+      </c>
+      <c r="W6">
+        <v>0.5510513089005235</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-4.669946591596728</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1187373766365077</v>
+      </c>
+      <c r="C7">
+        <v>269.0311296383663</v>
+      </c>
+      <c r="D7">
+        <v>287.8961296383663</v>
+      </c>
+      <c r="E7">
+        <v>-116.725</v>
+      </c>
+      <c r="F7">
+        <v>23.875</v>
+      </c>
+      <c r="G7">
+        <v>5.01</v>
+      </c>
+      <c r="H7">
+        <v>336.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>35.8</v>
+      </c>
+      <c r="K7">
+        <v>57.1</v>
+      </c>
+      <c r="L7">
+        <v>-21.3</v>
+      </c>
+      <c r="M7">
+        <v>5.701350000000001</v>
+      </c>
+      <c r="N7">
+        <v>-27.00135000000001</v>
+      </c>
+      <c r="O7">
+        <v>-7.560377999999999</v>
+      </c>
+      <c r="P7">
+        <v>-19.44097200000001</v>
+      </c>
+      <c r="Q7">
+        <v>37.65902799999999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.0992708676636703</v>
+      </c>
+      <c r="T7">
+        <v>1.022462133504514</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-1.046068036517667</v>
+      </c>
+      <c r="W7">
+        <v>0.4886010471204189</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-3.735957273277382</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1207373766365077</v>
+      </c>
+      <c r="C8">
+        <v>257.2317544916635</v>
+      </c>
+      <c r="D8">
+        <v>280.8717544916635</v>
+      </c>
+      <c r="E8">
+        <v>-111.95</v>
+      </c>
+      <c r="F8">
+        <v>28.65</v>
+      </c>
+      <c r="G8">
+        <v>5.01</v>
+      </c>
+      <c r="H8">
+        <v>336.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>35.8</v>
+      </c>
+      <c r="K8">
+        <v>57.1</v>
+      </c>
+      <c r="L8">
+        <v>-21.3</v>
+      </c>
+      <c r="M8">
+        <v>6.84162</v>
+      </c>
+      <c r="N8">
+        <v>-28.14162</v>
+      </c>
+      <c r="O8">
+        <v>-7.879653599999998</v>
+      </c>
+      <c r="P8">
+        <v>-20.26196640000001</v>
+      </c>
+      <c r="Q8">
+        <v>36.8380336</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09991417476647531</v>
+      </c>
+      <c r="T8">
+        <v>1.033339390243924</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-0.8717233637647223</v>
+      </c>
+      <c r="W8">
+        <v>0.4469675392670157</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-3.113297727731152</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1227373766365077</v>
+      </c>
+      <c r="C9">
+        <v>245.7669905056027</v>
+      </c>
+      <c r="D9">
+        <v>274.1819905056028</v>
+      </c>
+      <c r="E9">
+        <v>-107.175</v>
+      </c>
+      <c r="F9">
+        <v>33.425</v>
+      </c>
+      <c r="G9">
+        <v>5.01</v>
+      </c>
+      <c r="H9">
+        <v>336.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>35.8</v>
+      </c>
+      <c r="K9">
+        <v>57.1</v>
+      </c>
+      <c r="L9">
+        <v>-21.3</v>
+      </c>
+      <c r="M9">
+        <v>7.981890000000002</v>
+      </c>
+      <c r="N9">
+        <v>-29.28189</v>
+      </c>
+      <c r="O9">
+        <v>-8.198929199999998</v>
+      </c>
+      <c r="P9">
+        <v>-21.08296080000001</v>
+      </c>
+      <c r="Q9">
+        <v>36.0170392</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1005713164306309</v>
+      </c>
+      <c r="T9">
+        <v>1.044450566483105</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-0.7471914546554761</v>
+      </c>
+      <c r="W9">
+        <v>0.4172293193717277</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-2.668540909483844</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1247373766365077</v>
+      </c>
+      <c r="C10">
+        <v>234.6134847325748</v>
+      </c>
+      <c r="D10">
+        <v>267.8034847325748</v>
+      </c>
+      <c r="E10">
+        <v>-102.4</v>
+      </c>
+      <c r="F10">
+        <v>38.2</v>
+      </c>
+      <c r="G10">
+        <v>5.01</v>
+      </c>
+      <c r="H10">
+        <v>336.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>35.8</v>
+      </c>
+      <c r="K10">
+        <v>57.1</v>
+      </c>
+      <c r="L10">
+        <v>-21.3</v>
+      </c>
+      <c r="M10">
+        <v>9.122160000000001</v>
+      </c>
+      <c r="N10">
+        <v>-30.42216000000001</v>
+      </c>
+      <c r="O10">
+        <v>-8.518204799999999</v>
+      </c>
+      <c r="P10">
+        <v>-21.90395520000001</v>
+      </c>
+      <c r="Q10">
+        <v>35.1960448</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1012427437831378</v>
+      </c>
+      <c r="T10">
+        <v>1.055803290031835</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-0.6537925228235416</v>
+      </c>
+      <c r="W10">
+        <v>0.3949256544502617</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-2.334973295798364</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1267373766365077</v>
+      </c>
+      <c r="C11">
+        <v>223.7500079296706</v>
+      </c>
+      <c r="D11">
+        <v>261.7150079296706</v>
+      </c>
+      <c r="E11">
+        <v>-97.625</v>
+      </c>
+      <c r="F11">
+        <v>42.975</v>
+      </c>
+      <c r="G11">
+        <v>5.01</v>
+      </c>
+      <c r="H11">
+        <v>336.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>35.8</v>
+      </c>
+      <c r="K11">
+        <v>57.1</v>
+      </c>
+      <c r="L11">
+        <v>-21.3</v>
+      </c>
+      <c r="M11">
+        <v>10.26243</v>
+      </c>
+      <c r="N11">
+        <v>-31.56243000000001</v>
+      </c>
+      <c r="O11">
+        <v>-8.837480399999999</v>
+      </c>
+      <c r="P11">
+        <v>-22.72494960000001</v>
+      </c>
+      <c r="Q11">
+        <v>34.37505039999999</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1019289277807547</v>
+      </c>
+      <c r="T11">
+        <v>1.067405523988229</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-0.5811489091764815</v>
+      </c>
+      <c r="W11">
+        <v>0.3775783595113438</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-2.075531818487435</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1287373766365077</v>
+      </c>
+      <c r="C12">
+        <v>213.1572185143895</v>
+      </c>
+      <c r="D12">
+        <v>255.8972185143895</v>
+      </c>
+      <c r="E12">
+        <v>-92.84999999999999</v>
+      </c>
+      <c r="F12">
+        <v>47.75</v>
+      </c>
+      <c r="G12">
+        <v>5.01</v>
+      </c>
+      <c r="H12">
+        <v>336.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>35.8</v>
+      </c>
+      <c r="K12">
+        <v>57.1</v>
+      </c>
+      <c r="L12">
+        <v>-21.3</v>
+      </c>
+      <c r="M12">
+        <v>11.4027</v>
+      </c>
+      <c r="N12">
+        <v>-32.70270000000001</v>
+      </c>
+      <c r="O12">
+        <v>-9.156756</v>
+      </c>
+      <c r="P12">
+        <v>-23.54594400000001</v>
+      </c>
+      <c r="Q12">
+        <v>33.554056</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.102630360311652</v>
+      </c>
+      <c r="T12">
+        <v>1.079265585365876</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-0.5230340182588333</v>
+      </c>
+      <c r="W12">
+        <v>0.3637005235602094</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-1.867978636638691</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1307373766365077</v>
+      </c>
+      <c r="C13">
+        <v>202.817457318575</v>
+      </c>
+      <c r="D13">
+        <v>250.3324573185751</v>
+      </c>
+      <c r="E13">
+        <v>-88.07499999999999</v>
+      </c>
+      <c r="F13">
+        <v>52.525</v>
+      </c>
+      <c r="G13">
+        <v>5.01</v>
+      </c>
+      <c r="H13">
+        <v>336.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>35.8</v>
+      </c>
+      <c r="K13">
+        <v>57.1</v>
+      </c>
+      <c r="L13">
+        <v>-21.3</v>
+      </c>
+      <c r="M13">
+        <v>12.54297</v>
+      </c>
+      <c r="N13">
+        <v>-33.84297000000001</v>
+      </c>
+      <c r="O13">
+        <v>-9.476031599999999</v>
+      </c>
+      <c r="P13">
+        <v>-24.36693840000001</v>
+      </c>
+      <c r="Q13">
+        <v>32.73306159999999</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1033475553713335</v>
+      </c>
+      <c r="T13">
+        <v>1.091392164976728</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.475485471144394</v>
+      </c>
+      <c r="W13">
+        <v>0.3523459305092813</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-1.698162396944265</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1327373766365077</v>
+      </c>
+      <c r="C14">
+        <v>192.7145685521728</v>
+      </c>
+      <c r="D14">
+        <v>245.0045685521727</v>
+      </c>
+      <c r="E14">
+        <v>-83.3</v>
+      </c>
+      <c r="F14">
+        <v>57.3</v>
+      </c>
+      <c r="G14">
+        <v>5.01</v>
+      </c>
+      <c r="H14">
+        <v>336.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>35.8</v>
+      </c>
+      <c r="K14">
+        <v>57.1</v>
+      </c>
+      <c r="L14">
+        <v>-21.3</v>
+      </c>
+      <c r="M14">
+        <v>13.68324</v>
+      </c>
+      <c r="N14">
+        <v>-34.98324</v>
+      </c>
+      <c r="O14">
+        <v>-9.795307199999998</v>
+      </c>
+      <c r="P14">
+        <v>-25.18793280000001</v>
+      </c>
+      <c r="Q14">
+        <v>31.9120672</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.104081050318735</v>
+      </c>
+      <c r="T14">
+        <v>1.103794348669646</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.4358616818823611</v>
+      </c>
+      <c r="W14">
+        <v>0.3428837696335079</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-1.556648863865576</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1347373766365078</v>
+      </c>
+      <c r="C15">
+        <v>182.8337431533739</v>
+      </c>
+      <c r="D15">
+        <v>239.8987431533739</v>
+      </c>
+      <c r="E15">
+        <v>-78.52499999999999</v>
+      </c>
+      <c r="F15">
+        <v>62.075</v>
+      </c>
+      <c r="G15">
+        <v>5.01</v>
+      </c>
+      <c r="H15">
+        <v>336.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>35.8</v>
+      </c>
+      <c r="K15">
+        <v>57.1</v>
+      </c>
+      <c r="L15">
+        <v>-21.3</v>
+      </c>
+      <c r="M15">
+        <v>14.82351</v>
+      </c>
+      <c r="N15">
+        <v>-36.12351</v>
+      </c>
+      <c r="O15">
+        <v>-10.1145828</v>
+      </c>
+      <c r="P15">
+        <v>-26.00892720000001</v>
+      </c>
+      <c r="Q15">
+        <v>31.0910728</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1048314072189503</v>
+      </c>
+      <c r="T15">
+        <v>1.116481640033665</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.4023338601991026</v>
+      </c>
+      <c r="W15">
+        <v>0.3348773258155457</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-1.436906643568224</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1367373766365077</v>
+      </c>
+      <c r="C16">
+        <v>173.1613813261302</v>
+      </c>
+      <c r="D16">
+        <v>235.0013813261302</v>
+      </c>
+      <c r="E16">
+        <v>-73.74999999999999</v>
+      </c>
+      <c r="F16">
+        <v>66.85000000000001</v>
+      </c>
+      <c r="G16">
+        <v>5.01</v>
+      </c>
+      <c r="H16">
+        <v>336.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>35.8</v>
+      </c>
+      <c r="K16">
+        <v>57.1</v>
+      </c>
+      <c r="L16">
+        <v>-21.3</v>
+      </c>
+      <c r="M16">
+        <v>15.96378</v>
+      </c>
+      <c r="N16">
+        <v>-37.26378000000001</v>
+      </c>
+      <c r="O16">
+        <v>-10.4338584</v>
+      </c>
+      <c r="P16">
+        <v>-26.82992160000001</v>
+      </c>
+      <c r="Q16">
+        <v>30.27007839999999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1055992142796358</v>
+      </c>
+      <c r="T16">
+        <v>1.129463984685219</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.373595727327738</v>
+      </c>
+      <c r="W16">
+        <v>0.3280146596858639</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-1.334270454741922</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1387373766365077</v>
+      </c>
+      <c r="C17">
+        <v>163.6849715780165</v>
+      </c>
+      <c r="D17">
+        <v>230.2999715780165</v>
+      </c>
+      <c r="E17">
+        <v>-68.97499999999999</v>
+      </c>
+      <c r="F17">
+        <v>71.625</v>
+      </c>
+      <c r="G17">
+        <v>5.01</v>
+      </c>
+      <c r="H17">
+        <v>336.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>35.8</v>
+      </c>
+      <c r="K17">
+        <v>57.1</v>
+      </c>
+      <c r="L17">
+        <v>-21.3</v>
+      </c>
+      <c r="M17">
+        <v>17.10405</v>
+      </c>
+      <c r="N17">
+        <v>-38.40405000000001</v>
+      </c>
+      <c r="O17">
+        <v>-10.753134</v>
+      </c>
+      <c r="P17">
+        <v>-27.65091600000001</v>
+      </c>
+      <c r="Q17">
+        <v>29.44908399999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.106385087388808</v>
+      </c>
+      <c r="T17">
+        <v>1.142751796269751</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.3486893455058889</v>
+      </c>
+      <c r="W17">
+        <v>0.3220670157068063</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-1.245319091092461</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1407373766365077</v>
+      </c>
+      <c r="C18">
+        <v>154.3929839930373</v>
+      </c>
+      <c r="D18">
+        <v>225.7829839930373</v>
+      </c>
+      <c r="E18">
+        <v>-64.19999999999999</v>
+      </c>
+      <c r="F18">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="G18">
+        <v>5.01</v>
+      </c>
+      <c r="H18">
+        <v>336.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>35.8</v>
+      </c>
+      <c r="K18">
+        <v>57.1</v>
+      </c>
+      <c r="L18">
+        <v>-21.3</v>
+      </c>
+      <c r="M18">
+        <v>18.24432</v>
+      </c>
+      <c r="N18">
+        <v>-39.54432000000001</v>
+      </c>
+      <c r="O18">
+        <v>-11.0724096</v>
+      </c>
+      <c r="P18">
+        <v>-28.47191040000001</v>
+      </c>
+      <c r="Q18">
+        <v>28.6280896</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1071896717624843</v>
+      </c>
+      <c r="T18">
+        <v>1.156355984320581</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.3268962614117708</v>
+      </c>
+      <c r="W18">
+        <v>0.3168628272251309</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-1.167486647899182</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1427373766365077</v>
+      </c>
+      <c r="C19">
+        <v>145.274775822591</v>
+      </c>
+      <c r="D19">
+        <v>221.439775822591</v>
+      </c>
+      <c r="E19">
+        <v>-59.42499999999998</v>
+      </c>
+      <c r="F19">
+        <v>81.17500000000001</v>
+      </c>
+      <c r="G19">
+        <v>5.01</v>
+      </c>
+      <c r="H19">
+        <v>336.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>35.8</v>
+      </c>
+      <c r="K19">
+        <v>57.1</v>
+      </c>
+      <c r="L19">
+        <v>-21.3</v>
+      </c>
+      <c r="M19">
+        <v>19.38459</v>
+      </c>
+      <c r="N19">
+        <v>-40.68459000000001</v>
+      </c>
+      <c r="O19">
+        <v>-11.3916852</v>
+      </c>
+      <c r="P19">
+        <v>-29.29290480000001</v>
+      </c>
+      <c r="Q19">
+        <v>27.80709519999999</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1080136437114299</v>
+      </c>
+      <c r="T19">
+        <v>1.170287984131673</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.3076670695640196</v>
+      </c>
+      <c r="W19">
+        <v>0.3122708962118879</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-1.098810962728642</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1447373766365077</v>
+      </c>
+      <c r="C20">
+        <v>136.3205077672135</v>
+      </c>
+      <c r="D20">
+        <v>217.2605077672136</v>
+      </c>
+      <c r="E20">
+        <v>-54.64999999999999</v>
+      </c>
+      <c r="F20">
+        <v>85.95</v>
+      </c>
+      <c r="G20">
+        <v>5.01</v>
+      </c>
+      <c r="H20">
+        <v>336.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>35.8</v>
+      </c>
+      <c r="K20">
+        <v>57.1</v>
+      </c>
+      <c r="L20">
+        <v>-21.3</v>
+      </c>
+      <c r="M20">
+        <v>20.52486</v>
+      </c>
+      <c r="N20">
+        <v>-41.82486</v>
+      </c>
+      <c r="O20">
+        <v>-11.7109608</v>
+      </c>
+      <c r="P20">
+        <v>-30.11389920000001</v>
+      </c>
+      <c r="Q20">
+        <v>26.9861008</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.108857712537179</v>
+      </c>
+      <c r="T20">
+        <v>1.184559788816205</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.2905744545882408</v>
+      </c>
+      <c r="W20">
+        <v>0.3081891797556719</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-1.037765909243717</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1467373766365077</v>
+      </c>
+      <c r="C21">
+        <v>127.521069562885</v>
+      </c>
+      <c r="D21">
+        <v>213.236069562885</v>
+      </c>
+      <c r="E21">
+        <v>-49.875</v>
+      </c>
+      <c r="F21">
+        <v>90.72499999999999</v>
+      </c>
+      <c r="G21">
+        <v>5.01</v>
+      </c>
+      <c r="H21">
+        <v>336.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>35.8</v>
+      </c>
+      <c r="K21">
+        <v>57.1</v>
+      </c>
+      <c r="L21">
+        <v>-21.3</v>
+      </c>
+      <c r="M21">
+        <v>21.66513</v>
+      </c>
+      <c r="N21">
+        <v>-42.96513</v>
+      </c>
+      <c r="O21">
+        <v>-12.0302364</v>
+      </c>
+      <c r="P21">
+        <v>-30.93489360000001</v>
+      </c>
+      <c r="Q21">
+        <v>26.1651064</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1097226225685022</v>
+      </c>
+      <c r="T21">
+        <v>1.199183983739862</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.2752810622414912</v>
+      </c>
+      <c r="W21">
+        <v>0.3045371176632681</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-0.9831466508624689</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1487373766365077</v>
+      </c>
+      <c r="C22">
+        <v>118.8680136873619</v>
+      </c>
+      <c r="D22">
+        <v>209.3580136873619</v>
+      </c>
+      <c r="E22">
+        <v>-45.09999999999999</v>
+      </c>
+      <c r="F22">
+        <v>95.5</v>
+      </c>
+      <c r="G22">
+        <v>5.01</v>
+      </c>
+      <c r="H22">
+        <v>336.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>35.8</v>
+      </c>
+      <c r="K22">
+        <v>57.1</v>
+      </c>
+      <c r="L22">
+        <v>-21.3</v>
+      </c>
+      <c r="M22">
+        <v>22.8054</v>
+      </c>
+      <c r="N22">
+        <v>-44.1054</v>
+      </c>
+      <c r="O22">
+        <v>-12.349512</v>
+      </c>
+      <c r="P22">
+        <v>-31.75588800000001</v>
+      </c>
+      <c r="Q22">
+        <v>25.344112</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1106091553506085</v>
+      </c>
+      <c r="T22">
+        <v>1.21417378353661</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.2615170091294167</v>
+      </c>
+      <c r="W22">
+        <v>0.3012502617801047</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-0.9339893183193453</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1507373766365077</v>
+      </c>
+      <c r="C23">
+        <v>110.353496171269</v>
+      </c>
+      <c r="D23">
+        <v>205.618496171269</v>
+      </c>
+      <c r="E23">
+        <v>-40.325</v>
+      </c>
+      <c r="F23">
+        <v>100.275</v>
+      </c>
+      <c r="G23">
+        <v>5.01</v>
+      </c>
+      <c r="H23">
+        <v>336.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>35.8</v>
+      </c>
+      <c r="K23">
+        <v>57.1</v>
+      </c>
+      <c r="L23">
+        <v>-21.3</v>
+      </c>
+      <c r="M23">
+        <v>23.94567</v>
+      </c>
+      <c r="N23">
+        <v>-45.24567</v>
+      </c>
+      <c r="O23">
+        <v>-12.6687876</v>
+      </c>
+      <c r="P23">
+        <v>-32.5768824</v>
+      </c>
+      <c r="Q23">
+        <v>24.5231176</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1115181320006162</v>
+      </c>
+      <c r="T23">
+        <v>1.229543071935808</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.2490638182184921</v>
+      </c>
+      <c r="W23">
+        <v>0.2982764397905759</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-0.8895136364946148</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1527373766365077</v>
+      </c>
+      <c r="C24">
+        <v>101.9702236412085</v>
+      </c>
+      <c r="D24">
+        <v>202.0102236412085</v>
+      </c>
+      <c r="E24">
+        <v>-35.55</v>
+      </c>
+      <c r="F24">
+        <v>105.05</v>
+      </c>
+      <c r="G24">
+        <v>5.01</v>
+      </c>
+      <c r="H24">
+        <v>336.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>35.8</v>
+      </c>
+      <c r="K24">
+        <v>57.1</v>
+      </c>
+      <c r="L24">
+        <v>-21.3</v>
+      </c>
+      <c r="M24">
+        <v>25.08594</v>
+      </c>
+      <c r="N24">
+        <v>-46.38594000000001</v>
+      </c>
+      <c r="O24">
+        <v>-12.9880632</v>
+      </c>
+      <c r="P24">
+        <v>-33.39787680000001</v>
+      </c>
+      <c r="Q24">
+        <v>23.7021232</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1124504157442138</v>
+      </c>
+      <c r="T24">
+        <v>1.245306444652934</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.237742735572197</v>
+      </c>
+      <c r="W24">
+        <v>0.2955729652546407</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-0.8490811984721323</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1547373766365077</v>
+      </c>
+      <c r="C25">
+        <v>93.7114058425574</v>
+      </c>
+      <c r="D25">
+        <v>198.5264058425574</v>
+      </c>
+      <c r="E25">
+        <v>-30.77499999999999</v>
+      </c>
+      <c r="F25">
+        <v>109.825</v>
+      </c>
+      <c r="G25">
+        <v>5.01</v>
+      </c>
+      <c r="H25">
+        <v>336.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>35.8</v>
+      </c>
+      <c r="K25">
+        <v>57.1</v>
+      </c>
+      <c r="L25">
+        <v>-21.3</v>
+      </c>
+      <c r="M25">
+        <v>26.22621</v>
+      </c>
+      <c r="N25">
+        <v>-47.52621000000001</v>
+      </c>
+      <c r="O25">
+        <v>-13.3073388</v>
+      </c>
+      <c r="P25">
+        <v>-34.21887120000001</v>
+      </c>
+      <c r="Q25">
+        <v>22.88112879999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1134069146499828</v>
+      </c>
+      <c r="T25">
+        <v>1.261479255622452</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.2274060948951449</v>
+      </c>
+      <c r="W25">
+        <v>0.2931045754609606</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-0.8121646246255179</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1567373766365077</v>
+      </c>
+      <c r="C26">
+        <v>85.57071299165816</v>
+      </c>
+      <c r="D26">
+        <v>195.1607129916582</v>
+      </c>
+      <c r="E26">
+        <v>-26</v>
+      </c>
+      <c r="F26">
+        <v>114.6</v>
+      </c>
+      <c r="G26">
+        <v>5.01</v>
+      </c>
+      <c r="H26">
+        <v>336.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>35.8</v>
+      </c>
+      <c r="K26">
+        <v>57.1</v>
+      </c>
+      <c r="L26">
+        <v>-21.3</v>
+      </c>
+      <c r="M26">
+        <v>27.36648</v>
+      </c>
+      <c r="N26">
+        <v>-48.66648000000001</v>
+      </c>
+      <c r="O26">
+        <v>-13.6266144</v>
+      </c>
+      <c r="P26">
+        <v>-35.03986560000001</v>
+      </c>
+      <c r="Q26">
+        <v>22.06013439999999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1143885845795879</v>
+      </c>
+      <c r="T26">
+        <v>1.278077666880642</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.2179308409411806</v>
+      </c>
+      <c r="W26">
+        <v>0.2908418848167539</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-0.7783244319327882</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1587373766365077</v>
+      </c>
+      <c r="C27">
+        <v>77.54223739383517</v>
+      </c>
+      <c r="D27">
+        <v>191.9072373938352</v>
+      </c>
+      <c r="E27">
+        <v>-21.22499999999999</v>
+      </c>
+      <c r="F27">
+        <v>119.375</v>
+      </c>
+      <c r="G27">
+        <v>5.01</v>
+      </c>
+      <c r="H27">
+        <v>336.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>35.8</v>
+      </c>
+      <c r="K27">
+        <v>57.1</v>
+      </c>
+      <c r="L27">
+        <v>-21.3</v>
+      </c>
+      <c r="M27">
+        <v>28.50675</v>
+      </c>
+      <c r="N27">
+        <v>-49.80675000000001</v>
+      </c>
+      <c r="O27">
+        <v>-13.94589</v>
+      </c>
+      <c r="P27">
+        <v>-35.86086000000001</v>
+      </c>
+      <c r="Q27">
+        <v>21.23913999999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1153964323739824</v>
+      </c>
+      <c r="T27">
+        <v>1.295118702439051</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.2092136073035333</v>
+      </c>
+      <c r="W27">
+        <v>0.2887602094240838</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-0.7471914546554765</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1607373766365077</v>
+      </c>
+      <c r="C28">
+        <v>69.62045883759853</v>
+      </c>
+      <c r="D28">
+        <v>188.7604588375985</v>
+      </c>
+      <c r="E28">
+        <v>-16.44999999999999</v>
+      </c>
+      <c r="F28">
+        <v>124.15</v>
+      </c>
+      <c r="G28">
+        <v>5.01</v>
+      </c>
+      <c r="H28">
+        <v>336.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>35.8</v>
+      </c>
+      <c r="K28">
+        <v>57.1</v>
+      </c>
+      <c r="L28">
+        <v>-21.3</v>
+      </c>
+      <c r="M28">
+        <v>29.64702</v>
+      </c>
+      <c r="N28">
+        <v>-50.94702000000001</v>
+      </c>
+      <c r="O28">
+        <v>-14.2651656</v>
+      </c>
+      <c r="P28">
+        <v>-36.68185440000001</v>
+      </c>
+      <c r="Q28">
+        <v>20.41814559999999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1164315192979551</v>
+      </c>
+      <c r="T28">
+        <v>1.312620306526065</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.2011669300995513</v>
+      </c>
+      <c r="W28">
+        <v>0.2868386629077729</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-0.718453321784112</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1627373766365077</v>
+      </c>
+      <c r="C29">
+        <v>61.80021333858977</v>
+      </c>
+      <c r="D29">
+        <v>185.7152133385898</v>
+      </c>
+      <c r="E29">
+        <v>-11.67499999999998</v>
+      </c>
+      <c r="F29">
+        <v>128.925</v>
+      </c>
+      <c r="G29">
+        <v>5.01</v>
+      </c>
+      <c r="H29">
+        <v>336.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>35.8</v>
+      </c>
+      <c r="K29">
+        <v>57.1</v>
+      </c>
+      <c r="L29">
+        <v>-21.3</v>
+      </c>
+      <c r="M29">
+        <v>30.78729000000001</v>
+      </c>
+      <c r="N29">
+        <v>-52.08729000000001</v>
+      </c>
+      <c r="O29">
+        <v>-14.5844412</v>
+      </c>
+      <c r="P29">
+        <v>-37.50284880000001</v>
+      </c>
+      <c r="Q29">
+        <v>19.59715119999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1174949647677901</v>
+      </c>
+      <c r="T29">
+        <v>1.330601406615463</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.1937163030588271</v>
+      </c>
+      <c r="W29">
+        <v>0.285059453170448</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-0.6918439394958114</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1647373766365077</v>
+      </c>
+      <c r="C30">
+        <v>54.0766648609893</v>
+      </c>
+      <c r="D30">
+        <v>182.7666648609893</v>
+      </c>
+      <c r="E30">
+        <v>-6.899999999999977</v>
+      </c>
+      <c r="F30">
+        <v>133.7</v>
+      </c>
+      <c r="G30">
+        <v>5.01</v>
+      </c>
+      <c r="H30">
+        <v>336.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>35.8</v>
+      </c>
+      <c r="K30">
+        <v>57.1</v>
+      </c>
+      <c r="L30">
+        <v>-21.3</v>
+      </c>
+      <c r="M30">
+        <v>31.92756000000001</v>
+      </c>
+      <c r="N30">
+        <v>-53.22756000000001</v>
+      </c>
+      <c r="O30">
+        <v>-14.9037168</v>
+      </c>
+      <c r="P30">
+        <v>-38.32384320000001</v>
+      </c>
+      <c r="Q30">
+        <v>18.77615679999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.118587950389565</v>
+      </c>
+      <c r="T30">
+        <v>1.349081981707345</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.186797863663869</v>
+      </c>
+      <c r="W30">
+        <v>0.2834073298429319</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-0.667135227370961</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1667373766365077</v>
+      </c>
+      <c r="C31">
+        <v>46.44527969065109</v>
+      </c>
+      <c r="D31">
+        <v>179.9102796906511</v>
+      </c>
+      <c r="E31">
+        <v>-2.125</v>
+      </c>
+      <c r="F31">
+        <v>138.475</v>
+      </c>
+      <c r="G31">
+        <v>5.01</v>
+      </c>
+      <c r="H31">
+        <v>336.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>35.8</v>
+      </c>
+      <c r="K31">
+        <v>57.1</v>
+      </c>
+      <c r="L31">
+        <v>-21.3</v>
+      </c>
+      <c r="M31">
+        <v>33.06783</v>
+      </c>
+      <c r="N31">
+        <v>-54.36783</v>
+      </c>
+      <c r="O31">
+        <v>-15.2229924</v>
+      </c>
+      <c r="P31">
+        <v>-39.14483760000001</v>
+      </c>
+      <c r="Q31">
+        <v>17.95516239999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1197117243387138</v>
+      </c>
+      <c r="T31">
+        <v>1.368083136379279</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.1803565580202874</v>
+      </c>
+      <c r="W31">
+        <v>0.2818691460552447</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-0.6441305643581694</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1687373766365077</v>
+      </c>
+      <c r="C32">
+        <v>38.90180317432919</v>
+      </c>
+      <c r="D32">
+        <v>177.1418031743292</v>
+      </c>
+      <c r="E32">
+        <v>2.650000000000006</v>
+      </c>
+      <c r="F32">
+        <v>143.25</v>
+      </c>
+      <c r="G32">
+        <v>5.01</v>
+      </c>
+      <c r="H32">
+        <v>336.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>35.8</v>
+      </c>
+      <c r="K32">
+        <v>57.1</v>
+      </c>
+      <c r="L32">
+        <v>-21.3</v>
+      </c>
+      <c r="M32">
+        <v>34.2081</v>
+      </c>
+      <c r="N32">
+        <v>-55.50810000000001</v>
+      </c>
+      <c r="O32">
+        <v>-15.542268</v>
+      </c>
+      <c r="P32">
+        <v>-39.96583200000001</v>
+      </c>
+      <c r="Q32">
+        <v>17.134168</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1208676061149811</v>
+      </c>
+      <c r="T32">
+        <v>1.387627181184698</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.1743446727529445</v>
+      </c>
+      <c r="W32">
+        <v>0.2804335078534032</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-0.6226595455462303</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1707373766365077</v>
+      </c>
+      <c r="C33">
+        <v>31.44223857399103</v>
+      </c>
+      <c r="D33">
+        <v>174.457238573991</v>
+      </c>
+      <c r="E33">
+        <v>7.425000000000011</v>
+      </c>
+      <c r="F33">
+        <v>148.025</v>
+      </c>
+      <c r="G33">
+        <v>5.01</v>
+      </c>
+      <c r="H33">
+        <v>336.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>35.8</v>
+      </c>
+      <c r="K33">
+        <v>57.1</v>
+      </c>
+      <c r="L33">
+        <v>-21.3</v>
+      </c>
+      <c r="M33">
+        <v>35.34837</v>
+      </c>
+      <c r="N33">
+        <v>-56.64837000000001</v>
+      </c>
+      <c r="O33">
+        <v>-15.8615436</v>
+      </c>
+      <c r="P33">
+        <v>-40.78682640000001</v>
+      </c>
+      <c r="Q33">
+        <v>16.31317359999999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1220569917108504</v>
+      </c>
+      <c r="T33">
+        <v>1.407737720042447</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.1687206510512366</v>
+      </c>
+      <c r="W33">
+        <v>0.2790904914710353</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-0.6025737537544165</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1727373766365077</v>
+      </c>
+      <c r="C34">
+        <v>24.06282781518979</v>
+      </c>
+      <c r="D34">
+        <v>171.8528278151898</v>
+      </c>
+      <c r="E34">
+        <v>12.20000000000002</v>
+      </c>
+      <c r="F34">
+        <v>152.8</v>
+      </c>
+      <c r="G34">
+        <v>5.01</v>
+      </c>
+      <c r="H34">
+        <v>336.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>35.8</v>
+      </c>
+      <c r="K34">
+        <v>57.1</v>
+      </c>
+      <c r="L34">
+        <v>-21.3</v>
+      </c>
+      <c r="M34">
+        <v>36.48864</v>
+      </c>
+      <c r="N34">
+        <v>-57.78864000000001</v>
+      </c>
+      <c r="O34">
+        <v>-16.1808192</v>
+      </c>
+      <c r="P34">
+        <v>-41.60782080000001</v>
+      </c>
+      <c r="Q34">
+        <v>15.49217919999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.12328135923601</v>
+      </c>
+      <c r="T34">
+        <v>1.428439745337188</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.1634481307058854</v>
+      </c>
+      <c r="W34">
+        <v>0.2778314136125655</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-0.5837433239495911</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1747373766365077</v>
+      </c>
+      <c r="C35">
+        <v>16.76003393447726</v>
+      </c>
+      <c r="D35">
+        <v>169.3250339344773</v>
+      </c>
+      <c r="E35">
+        <v>16.97500000000002</v>
+      </c>
+      <c r="F35">
+        <v>157.575</v>
+      </c>
+      <c r="G35">
+        <v>5.01</v>
+      </c>
+      <c r="H35">
+        <v>336.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>35.8</v>
+      </c>
+      <c r="K35">
+        <v>57.1</v>
+      </c>
+      <c r="L35">
+        <v>-21.3</v>
+      </c>
+      <c r="M35">
+        <v>37.62891</v>
+      </c>
+      <c r="N35">
+        <v>-58.92891000000001</v>
+      </c>
+      <c r="O35">
+        <v>-16.5000948</v>
+      </c>
+      <c r="P35">
+        <v>-42.42881520000002</v>
+      </c>
+      <c r="Q35">
+        <v>14.67118479999998</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1245422750455027</v>
+      </c>
+      <c r="T35">
+        <v>1.449759741536251</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.1584951570481313</v>
+      </c>
+      <c r="W35">
+        <v>0.2766486435030938</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-0.5660541323147548</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1767373766365077</v>
+      </c>
+      <c r="C36">
+        <v>9.530525053453687</v>
+      </c>
+      <c r="D36">
+        <v>166.8705250534537</v>
+      </c>
+      <c r="E36">
+        <v>21.75000000000003</v>
+      </c>
+      <c r="F36">
+        <v>162.35</v>
+      </c>
+      <c r="G36">
+        <v>5.01</v>
+      </c>
+      <c r="H36">
+        <v>336.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>35.8</v>
+      </c>
+      <c r="K36">
+        <v>57.1</v>
+      </c>
+      <c r="L36">
+        <v>-21.3</v>
+      </c>
+      <c r="M36">
+        <v>38.76918000000001</v>
+      </c>
+      <c r="N36">
+        <v>-60.06918000000001</v>
+      </c>
+      <c r="O36">
+        <v>-16.8193704</v>
+      </c>
+      <c r="P36">
+        <v>-43.24980960000001</v>
+      </c>
+      <c r="Q36">
+        <v>13.85019039999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.12584140042498</v>
+      </c>
+      <c r="T36">
+        <v>1.471725798226194</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.1538335347820098</v>
+      </c>
+      <c r="W36">
+        <v>0.275535448105944</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-0.5494054813643208</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1787373766365077</v>
+      </c>
+      <c r="C37">
+        <v>2.371159726758862</v>
+      </c>
+      <c r="D37">
+        <v>164.4861597267589</v>
+      </c>
+      <c r="E37">
+        <v>26.52500000000003</v>
+      </c>
+      <c r="F37">
+        <v>167.125</v>
+      </c>
+      <c r="G37">
+        <v>5.01</v>
+      </c>
+      <c r="H37">
+        <v>336.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>35.8</v>
+      </c>
+      <c r="K37">
+        <v>57.1</v>
+      </c>
+      <c r="L37">
+        <v>-21.3</v>
+      </c>
+      <c r="M37">
+        <v>39.90945000000001</v>
+      </c>
+      <c r="N37">
+        <v>-61.20945000000001</v>
+      </c>
+      <c r="O37">
+        <v>-17.138646</v>
+      </c>
+      <c r="P37">
+        <v>-44.07080400000001</v>
+      </c>
+      <c r="Q37">
+        <v>13.02919599999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1271804988930566</v>
+      </c>
+      <c r="T37">
+        <v>1.49436773358352</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.1494382909310952</v>
+      </c>
+      <c r="W37">
+        <v>0.2744858638743455</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-0.5337081818967688</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1807373766365077</v>
+      </c>
+      <c r="C38">
+        <v>-4.721026471482134</v>
+      </c>
+      <c r="D38">
+        <v>162.1689735285179</v>
+      </c>
+      <c r="E38">
+        <v>31.30000000000001</v>
+      </c>
+      <c r="F38">
+        <v>171.9</v>
+      </c>
+      <c r="G38">
+        <v>5.01</v>
+      </c>
+      <c r="H38">
+        <v>336.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>35.8</v>
+      </c>
+      <c r="K38">
+        <v>57.1</v>
+      </c>
+      <c r="L38">
+        <v>-21.3</v>
+      </c>
+      <c r="M38">
+        <v>41.04972</v>
+      </c>
+      <c r="N38">
+        <v>-62.34972</v>
+      </c>
+      <c r="O38">
+        <v>-17.4579216</v>
+      </c>
+      <c r="P38">
+        <v>-44.89179840000001</v>
+      </c>
+      <c r="Q38">
+        <v>12.20820159999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1285614441882606</v>
+      </c>
+      <c r="T38">
+        <v>1.517717229420763</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.1452872272941204</v>
+      </c>
+      <c r="W38">
+        <v>0.273494589877836</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-0.5188829546218587</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1827373766365077</v>
+      </c>
+      <c r="C39">
+        <v>-11.74883324318893</v>
+      </c>
+      <c r="D39">
+        <v>159.9161667568111</v>
+      </c>
+      <c r="E39">
+        <v>36.07500000000002</v>
+      </c>
+      <c r="F39">
+        <v>176.675</v>
+      </c>
+      <c r="G39">
+        <v>5.01</v>
+      </c>
+      <c r="H39">
+        <v>336.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>35.8</v>
+      </c>
+      <c r="K39">
+        <v>57.1</v>
+      </c>
+      <c r="L39">
+        <v>-21.3</v>
+      </c>
+      <c r="M39">
+        <v>42.18999</v>
+      </c>
+      <c r="N39">
+        <v>-63.48999000000001</v>
+      </c>
+      <c r="O39">
+        <v>-17.7771972</v>
+      </c>
+      <c r="P39">
+        <v>-45.71279280000001</v>
+      </c>
+      <c r="Q39">
+        <v>11.38720719999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1299862290166457</v>
+      </c>
+      <c r="T39">
+        <v>1.541807979094108</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.1413605454753604</v>
+      </c>
+      <c r="W39">
+        <v>0.2725568982595161</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-0.5048590909834301</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1847373766365077</v>
+      </c>
+      <c r="C40">
+        <v>-18.71490685106079</v>
+      </c>
+      <c r="D40">
+        <v>157.7250931489392</v>
+      </c>
+      <c r="E40">
+        <v>40.84999999999999</v>
+      </c>
+      <c r="F40">
+        <v>181.45</v>
+      </c>
+      <c r="G40">
+        <v>5.01</v>
+      </c>
+      <c r="H40">
+        <v>336.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>35.8</v>
+      </c>
+      <c r="K40">
+        <v>57.1</v>
+      </c>
+      <c r="L40">
+        <v>-21.3</v>
+      </c>
+      <c r="M40">
+        <v>43.33026</v>
+      </c>
+      <c r="N40">
+        <v>-64.63026000000001</v>
+      </c>
+      <c r="O40">
+        <v>-18.0964728</v>
+      </c>
+      <c r="P40">
+        <v>-46.53378720000001</v>
+      </c>
+      <c r="Q40">
+        <v>10.5662128</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1314569746459464</v>
+      </c>
+      <c r="T40">
+        <v>1.566675849724658</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.1376405311207456</v>
+      </c>
+      <c r="W40">
+        <v>0.271668558831634</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.4915733254312344</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1867373766365077</v>
+      </c>
+      <c r="C41">
+        <v>-25.62175048815149</v>
+      </c>
+      <c r="D41">
+        <v>155.5932495118485</v>
+      </c>
+      <c r="E41">
+        <v>45.625</v>
+      </c>
+      <c r="F41">
+        <v>186.225</v>
+      </c>
+      <c r="G41">
+        <v>5.01</v>
+      </c>
+      <c r="H41">
+        <v>336.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>35.8</v>
+      </c>
+      <c r="K41">
+        <v>57.1</v>
+      </c>
+      <c r="L41">
+        <v>-21.3</v>
+      </c>
+      <c r="M41">
+        <v>44.47053</v>
+      </c>
+      <c r="N41">
+        <v>-65.77053000000001</v>
+      </c>
+      <c r="O41">
+        <v>-18.4157484</v>
+      </c>
+      <c r="P41">
+        <v>-47.35478160000001</v>
+      </c>
+      <c r="Q41">
+        <v>9.745218399999992</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.132975941443421</v>
+      </c>
+      <c r="T41">
+        <v>1.592359060375882</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.1341112867330342</v>
+      </c>
+      <c r="W41">
+        <v>0.2708257752718485</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.4789688811894079</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1887373766365077</v>
+      </c>
+      <c r="C42">
+        <v>-32.47173381771501</v>
+      </c>
+      <c r="D42">
+        <v>153.518266182285</v>
+      </c>
+      <c r="E42">
+        <v>50.40000000000001</v>
+      </c>
+      <c r="F42">
+        <v>191</v>
+      </c>
+      <c r="G42">
+        <v>5.01</v>
+      </c>
+      <c r="H42">
+        <v>336.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>35.8</v>
+      </c>
+      <c r="K42">
+        <v>57.1</v>
+      </c>
+      <c r="L42">
+        <v>-21.3</v>
+      </c>
+      <c r="M42">
+        <v>45.6108</v>
+      </c>
+      <c r="N42">
+        <v>-66.91080000000001</v>
+      </c>
+      <c r="O42">
+        <v>-18.735024</v>
+      </c>
+      <c r="P42">
+        <v>-48.17577600000001</v>
+      </c>
+      <c r="Q42">
+        <v>8.924223999999988</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.134545540467478</v>
+      </c>
+      <c r="T42">
+        <v>1.618898378048814</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.1307585045647083</v>
+      </c>
+      <c r="W42">
+        <v>0.2700251308900524</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.4669946591596728</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1907373766365077</v>
+      </c>
+      <c r="C43">
+        <v>-39.26710175976035</v>
+      </c>
+      <c r="D43">
+        <v>151.4978982402397</v>
+      </c>
+      <c r="E43">
+        <v>55.17500000000001</v>
+      </c>
+      <c r="F43">
+        <v>195.775</v>
+      </c>
+      <c r="G43">
+        <v>5.01</v>
+      </c>
+      <c r="H43">
+        <v>336.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>35.8</v>
+      </c>
+      <c r="K43">
+        <v>57.1</v>
+      </c>
+      <c r="L43">
+        <v>-21.3</v>
+      </c>
+      <c r="M43">
+        <v>46.75107000000001</v>
+      </c>
+      <c r="N43">
+        <v>-68.05107000000001</v>
+      </c>
+      <c r="O43">
+        <v>-19.0542996</v>
+      </c>
+      <c r="P43">
+        <v>-48.99677040000002</v>
+      </c>
+      <c r="Q43">
+        <v>8.103229599999985</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1361683462381132</v>
+      </c>
+      <c r="T43">
+        <v>1.646337333608963</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.1275692727460569</v>
+      </c>
+      <c r="W43">
+        <v>0.2692635423317584</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.455604545521632</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1927373766365078</v>
+      </c>
+      <c r="C44">
+        <v>-46.00998259280897</v>
+      </c>
+      <c r="D44">
+        <v>149.530017407191</v>
+      </c>
+      <c r="E44">
+        <v>59.94999999999999</v>
+      </c>
+      <c r="F44">
+        <v>200.55</v>
+      </c>
+      <c r="G44">
+        <v>5.01</v>
+      </c>
+      <c r="H44">
+        <v>336.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>35.8</v>
+      </c>
+      <c r="K44">
+        <v>57.1</v>
+      </c>
+      <c r="L44">
+        <v>-21.3</v>
+      </c>
+      <c r="M44">
+        <v>47.89134</v>
+      </c>
+      <c r="N44">
+        <v>-69.19134</v>
+      </c>
+      <c r="O44">
+        <v>-19.37357519999999</v>
+      </c>
+      <c r="P44">
+        <v>-49.81776480000001</v>
+      </c>
+      <c r="Q44">
+        <v>7.282235199999995</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1378471108284255</v>
+      </c>
+      <c r="T44">
+        <v>1.674722460050497</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.1245319091092461</v>
+      </c>
+      <c r="W44">
+        <v>0.268538219895288</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.4447568182473074</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1947373766365078</v>
+      </c>
+      <c r="C45">
+        <v>-52.70239543232228</v>
+      </c>
+      <c r="D45">
+        <v>147.6126045676777</v>
+      </c>
+      <c r="E45">
+        <v>64.72499999999999</v>
+      </c>
+      <c r="F45">
+        <v>205.325</v>
+      </c>
+      <c r="G45">
+        <v>5.01</v>
+      </c>
+      <c r="H45">
+        <v>336.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>35.8</v>
+      </c>
+      <c r="K45">
+        <v>57.1</v>
+      </c>
+      <c r="L45">
+        <v>-21.3</v>
+      </c>
+      <c r="M45">
+        <v>49.03161</v>
+      </c>
+      <c r="N45">
+        <v>-70.33161000000001</v>
+      </c>
+      <c r="O45">
+        <v>-19.6928508</v>
+      </c>
+      <c r="P45">
+        <v>-50.63875920000001</v>
+      </c>
+      <c r="Q45">
+        <v>6.461240799999992</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1395847794394505</v>
+      </c>
+      <c r="T45">
+        <v>1.704103555840856</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.1216358181997287</v>
+      </c>
+      <c r="W45">
+        <v>0.2678466333860953</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.4344136364276028</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1967373766365077</v>
+      </c>
+      <c r="C46">
+        <v>-59.34625714104197</v>
+      </c>
+      <c r="D46">
+        <v>145.743742858958</v>
+      </c>
+      <c r="E46">
+        <v>69.5</v>
+      </c>
+      <c r="F46">
+        <v>210.1</v>
+      </c>
+      <c r="G46">
+        <v>5.01</v>
+      </c>
+      <c r="H46">
+        <v>336.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>35.8</v>
+      </c>
+      <c r="K46">
+        <v>57.1</v>
+      </c>
+      <c r="L46">
+        <v>-21.3</v>
+      </c>
+      <c r="M46">
+        <v>50.17188</v>
+      </c>
+      <c r="N46">
+        <v>-71.47188</v>
+      </c>
+      <c r="O46">
+        <v>-20.01212639999999</v>
+      </c>
+      <c r="P46">
+        <v>-51.45975360000001</v>
+      </c>
+      <c r="Q46">
+        <v>5.640246399999995</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1413845076437264</v>
+      </c>
+      <c r="T46">
+        <v>1.734533976480872</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.1188713677860985</v>
+      </c>
+      <c r="W46">
+        <v>0.2671864826273203</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.424540599236066</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1987373766365077</v>
+      </c>
+      <c r="C47">
+        <v>-65.94338872095955</v>
+      </c>
+      <c r="D47">
+        <v>143.9216112790405</v>
+      </c>
+      <c r="E47">
+        <v>74.27500000000001</v>
+      </c>
+      <c r="F47">
+        <v>214.875</v>
+      </c>
+      <c r="G47">
+        <v>5.01</v>
+      </c>
+      <c r="H47">
+        <v>336.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>35.8</v>
+      </c>
+      <c r="K47">
+        <v>57.1</v>
+      </c>
+      <c r="L47">
+        <v>-21.3</v>
+      </c>
+      <c r="M47">
+        <v>51.31215</v>
+      </c>
+      <c r="N47">
+        <v>-72.61215000000001</v>
+      </c>
+      <c r="O47">
+        <v>-20.331402</v>
+      </c>
+      <c r="P47">
+        <v>-52.28074800000002</v>
+      </c>
+      <c r="Q47">
+        <v>4.819251999999985</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.143249680509976</v>
+      </c>
+      <c r="T47">
+        <v>1.766070957871433</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.1162297818352963</v>
+      </c>
+      <c r="W47">
+        <v>0.2665556719022688</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.415106363697487</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2007373766365077</v>
+      </c>
+      <c r="C48">
+        <v>-72.49552123172026</v>
+      </c>
+      <c r="D48">
+        <v>142.1444787682798</v>
+      </c>
+      <c r="E48">
+        <v>79.05000000000001</v>
+      </c>
+      <c r="F48">
+        <v>219.65</v>
+      </c>
+      <c r="G48">
+        <v>5.01</v>
+      </c>
+      <c r="H48">
+        <v>336.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>35.8</v>
+      </c>
+      <c r="K48">
+        <v>57.1</v>
+      </c>
+      <c r="L48">
+        <v>-21.3</v>
+      </c>
+      <c r="M48">
+        <v>52.45242</v>
+      </c>
+      <c r="N48">
+        <v>-73.75242</v>
+      </c>
+      <c r="O48">
+        <v>-20.65067759999999</v>
+      </c>
+      <c r="P48">
+        <v>-53.10174240000001</v>
+      </c>
+      <c r="Q48">
+        <v>3.998257599999995</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1451839338527533</v>
+      </c>
+      <c r="T48">
+        <v>1.798775975609793</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.1137030474475725</v>
+      </c>
+      <c r="W48">
+        <v>0.2659522877304803</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.4060823123127588</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2027373766365078</v>
+      </c>
+      <c r="C49">
+        <v>-79.0043012758961</v>
+      </c>
+      <c r="D49">
+        <v>140.4106987241039</v>
+      </c>
+      <c r="E49">
+        <v>83.82500000000002</v>
+      </c>
+      <c r="F49">
+        <v>224.425</v>
+      </c>
+      <c r="G49">
+        <v>5.01</v>
+      </c>
+      <c r="H49">
+        <v>336.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>35.8</v>
+      </c>
+      <c r="K49">
+        <v>57.1</v>
+      </c>
+      <c r="L49">
+        <v>-21.3</v>
+      </c>
+      <c r="M49">
+        <v>53.59269</v>
+      </c>
+      <c r="N49">
+        <v>-74.89269000000002</v>
+      </c>
+      <c r="O49">
+        <v>-20.9699532</v>
+      </c>
+      <c r="P49">
+        <v>-53.92273680000002</v>
+      </c>
+      <c r="Q49">
+        <v>3.177263199999985</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1471911778877109</v>
+      </c>
+      <c r="T49">
+        <v>1.832715144960921</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.1112838336720922</v>
+      </c>
+      <c r="W49">
+        <v>0.2653745794808957</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.3974422631146153</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2047373766365078</v>
+      </c>
+      <c r="C50">
+        <v>-85.47129608766227</v>
+      </c>
+      <c r="D50">
+        <v>138.7187039123377</v>
+      </c>
+      <c r="E50">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="F50">
+        <v>229.2</v>
+      </c>
+      <c r="G50">
+        <v>5.01</v>
+      </c>
+      <c r="H50">
+        <v>336.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>35.8</v>
+      </c>
+      <c r="K50">
+        <v>57.1</v>
+      </c>
+      <c r="L50">
+        <v>-21.3</v>
+      </c>
+      <c r="M50">
+        <v>54.73296</v>
+      </c>
+      <c r="N50">
+        <v>-76.03296</v>
+      </c>
+      <c r="O50">
+        <v>-21.28922879999999</v>
+      </c>
+      <c r="P50">
+        <v>-54.74373120000001</v>
+      </c>
+      <c r="Q50">
+        <v>2.356268799999988</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1492756236163207</v>
+      </c>
+      <c r="T50">
+        <v>1.867959666979401</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.1089654204705903</v>
+      </c>
+      <c r="W50">
+        <v>0.264820942408377</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.3891622159663941</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2067373766365078</v>
+      </c>
+      <c r="C51">
+        <v>-91.89799825793369</v>
+      </c>
+      <c r="D51">
+        <v>137.0670017420663</v>
+      </c>
+      <c r="E51">
+        <v>93.375</v>
+      </c>
+      <c r="F51">
+        <v>233.975</v>
+      </c>
+      <c r="G51">
+        <v>5.01</v>
+      </c>
+      <c r="H51">
+        <v>336.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>35.8</v>
+      </c>
+      <c r="K51">
+        <v>57.1</v>
+      </c>
+      <c r="L51">
+        <v>-21.3</v>
+      </c>
+      <c r="M51">
+        <v>55.87323</v>
+      </c>
+      <c r="N51">
+        <v>-77.17323</v>
+      </c>
+      <c r="O51">
+        <v>-21.60850439999999</v>
+      </c>
+      <c r="P51">
+        <v>-55.56472560000001</v>
+      </c>
+      <c r="Q51">
+        <v>1.535274399999992</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.15144181231468</v>
+      </c>
+      <c r="T51">
+        <v>1.904586327116251</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.1067416363793538</v>
+      </c>
+      <c r="W51">
+        <v>0.2642899027673897</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.3812201299262634</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2087373766365077</v>
+      </c>
+      <c r="C52">
+        <v>-98.28583012590397</v>
+      </c>
+      <c r="D52">
+        <v>135.454169874096</v>
+      </c>
+      <c r="E52">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="F52">
+        <v>238.75</v>
+      </c>
+      <c r="G52">
+        <v>5.01</v>
+      </c>
+      <c r="H52">
+        <v>336.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>35.8</v>
+      </c>
+      <c r="K52">
+        <v>57.1</v>
+      </c>
+      <c r="L52">
+        <v>-21.3</v>
+      </c>
+      <c r="M52">
+        <v>57.0135</v>
+      </c>
+      <c r="N52">
+        <v>-78.3135</v>
+      </c>
+      <c r="O52">
+        <v>-21.92777999999999</v>
+      </c>
+      <c r="P52">
+        <v>-56.38572000000001</v>
+      </c>
+      <c r="Q52">
+        <v>0.7142799999999951</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1536946485609736</v>
+      </c>
+      <c r="T52">
+        <v>1.942678053658577</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.1046068036517667</v>
+      </c>
+      <c r="W52">
+        <v>0.2637801047120419</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.3735957273277382</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2107373766365077</v>
+      </c>
+      <c r="C53">
+        <v>-104.6361478641465</v>
+      </c>
+      <c r="D53">
+        <v>133.8788521358535</v>
+      </c>
+      <c r="E53">
+        <v>102.925</v>
+      </c>
+      <c r="F53">
+        <v>243.525</v>
+      </c>
+      <c r="G53">
+        <v>5.01</v>
+      </c>
+      <c r="H53">
+        <v>336.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>35.8</v>
+      </c>
+      <c r="K53">
+        <v>57.1</v>
+      </c>
+      <c r="L53">
+        <v>-21.3</v>
+      </c>
+      <c r="M53">
+        <v>58.15377</v>
+      </c>
+      <c r="N53">
+        <v>-79.45377000000001</v>
+      </c>
+      <c r="O53">
+        <v>-22.2470556</v>
+      </c>
+      <c r="P53">
+        <v>-57.20671440000001</v>
+      </c>
+      <c r="Q53">
+        <v>-0.1067144000000084</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1560394373071159</v>
+      </c>
+      <c r="T53">
+        <v>1.982324544549568</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.1025556898546732</v>
+      </c>
+      <c r="W53">
+        <v>0.263290298737296</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.3662703209095473</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2127373766365077</v>
+      </c>
+      <c r="C54">
+        <v>-110.9502452819358</v>
+      </c>
+      <c r="D54">
+        <v>132.3397547180642</v>
+      </c>
+      <c r="E54">
+        <v>107.7</v>
+      </c>
+      <c r="F54">
+        <v>248.3</v>
+      </c>
+      <c r="G54">
+        <v>5.01</v>
+      </c>
+      <c r="H54">
+        <v>336.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>35.8</v>
+      </c>
+      <c r="K54">
+        <v>57.1</v>
+      </c>
+      <c r="L54">
+        <v>-21.3</v>
+      </c>
+      <c r="M54">
+        <v>59.29404</v>
+      </c>
+      <c r="N54">
+        <v>-80.59404000000001</v>
+      </c>
+      <c r="O54">
+        <v>-22.56633119999999</v>
+      </c>
+      <c r="P54">
+        <v>-58.02770880000001</v>
+      </c>
+      <c r="Q54">
+        <v>-0.927708800000012</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1584819255843475</v>
+      </c>
+      <c r="T54">
+        <v>2.023622972561017</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.1005834650497756</v>
+      </c>
+      <c r="W54">
+        <v>0.2628193314538864</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.359226660892056</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2147373766365078</v>
+      </c>
+      <c r="C55">
+        <v>-117.2293573692096</v>
+      </c>
+      <c r="D55">
+        <v>130.8356426307904</v>
+      </c>
+      <c r="E55">
+        <v>112.475</v>
+      </c>
+      <c r="F55">
+        <v>253.075</v>
+      </c>
+      <c r="G55">
+        <v>5.01</v>
+      </c>
+      <c r="H55">
+        <v>336.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>35.8</v>
+      </c>
+      <c r="K55">
+        <v>57.1</v>
+      </c>
+      <c r="L55">
+        <v>-21.3</v>
+      </c>
+      <c r="M55">
+        <v>60.43431000000001</v>
+      </c>
+      <c r="N55">
+        <v>-81.73431000000002</v>
+      </c>
+      <c r="O55">
+        <v>-22.8856068</v>
+      </c>
+      <c r="P55">
+        <v>-58.84870320000002</v>
+      </c>
+      <c r="Q55">
+        <v>-1.748703200000023</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1610283495329506</v>
+      </c>
+      <c r="T55">
+        <v>2.066678780487847</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.09868566382242137</v>
+      </c>
+      <c r="W55">
+        <v>0.2623661365207943</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.3524487993657908</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2167373766365077</v>
+      </c>
+      <c r="C56">
+        <v>-123.4746636015707</v>
+      </c>
+      <c r="D56">
+        <v>129.3653363984293</v>
+      </c>
+      <c r="E56">
+        <v>117.25</v>
+      </c>
+      <c r="F56">
+        <v>257.85</v>
+      </c>
+      <c r="G56">
+        <v>5.01</v>
+      </c>
+      <c r="H56">
+        <v>336.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>35.8</v>
+      </c>
+      <c r="K56">
+        <v>57.1</v>
+      </c>
+      <c r="L56">
+        <v>-21.3</v>
+      </c>
+      <c r="M56">
+        <v>61.57458000000001</v>
+      </c>
+      <c r="N56">
+        <v>-82.87458000000001</v>
+      </c>
+      <c r="O56">
+        <v>-23.2048824</v>
+      </c>
+      <c r="P56">
+        <v>-59.66969760000001</v>
+      </c>
+      <c r="Q56">
+        <v>-2.569697600000012</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1636854875662757</v>
+      </c>
+      <c r="T56">
+        <v>2.11160658006367</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.09685815152941357</v>
+      </c>
+      <c r="W56">
+        <v>0.261929726585224</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.3459219697479057</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2187373766365078</v>
+      </c>
+      <c r="C57">
+        <v>-129.6872910249213</v>
+      </c>
+      <c r="D57">
+        <v>127.9277089750787</v>
+      </c>
+      <c r="E57">
+        <v>122.025</v>
+      </c>
+      <c r="F57">
+        <v>262.625</v>
+      </c>
+      <c r="G57">
+        <v>5.01</v>
+      </c>
+      <c r="H57">
+        <v>336.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>35.8</v>
+      </c>
+      <c r="K57">
+        <v>57.1</v>
+      </c>
+      <c r="L57">
+        <v>-21.3</v>
+      </c>
+      <c r="M57">
+        <v>62.71485000000001</v>
+      </c>
+      <c r="N57">
+        <v>-84.01485000000001</v>
+      </c>
+      <c r="O57">
+        <v>-23.524158</v>
+      </c>
+      <c r="P57">
+        <v>-60.49069200000001</v>
+      </c>
+      <c r="Q57">
+        <v>-3.390692000000008</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.166460720623304</v>
+      </c>
+      <c r="T57">
+        <v>2.158531170731752</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.0950970942288788</v>
+      </c>
+      <c r="W57">
+        <v>0.2615091861018563</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.339632479388853</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2207373766365077</v>
+      </c>
+      <c r="C58">
+        <v>-135.8683171366811</v>
+      </c>
+      <c r="D58">
+        <v>126.5216828633189</v>
+      </c>
+      <c r="E58">
+        <v>126.8</v>
+      </c>
+      <c r="F58">
+        <v>267.4</v>
+      </c>
+      <c r="G58">
+        <v>5.01</v>
+      </c>
+      <c r="H58">
+        <v>336.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>35.8</v>
+      </c>
+      <c r="K58">
+        <v>57.1</v>
+      </c>
+      <c r="L58">
+        <v>-21.3</v>
+      </c>
+      <c r="M58">
+        <v>63.85512000000001</v>
+      </c>
+      <c r="N58">
+        <v>-85.15512000000001</v>
+      </c>
+      <c r="O58">
+        <v>-23.8434336</v>
+      </c>
+      <c r="P58">
+        <v>-61.31168640000001</v>
+      </c>
+      <c r="Q58">
+        <v>-4.211686400000012</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.16936210063747</v>
+      </c>
+      <c r="T58">
+        <v>2.207588697339292</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.09339893183193451</v>
+      </c>
+      <c r="W58">
+        <v>0.261103664921466</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.3335676136854804</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2227373766365077</v>
+      </c>
+      <c r="C59">
+        <v>-142.0187725790695</v>
+      </c>
+      <c r="D59">
+        <v>125.1462274209305</v>
+      </c>
+      <c r="E59">
+        <v>131.575</v>
+      </c>
+      <c r="F59">
+        <v>272.175</v>
+      </c>
+      <c r="G59">
+        <v>5.01</v>
+      </c>
+      <c r="H59">
+        <v>336.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>35.8</v>
+      </c>
+      <c r="K59">
+        <v>57.1</v>
+      </c>
+      <c r="L59">
+        <v>-21.3</v>
+      </c>
+      <c r="M59">
+        <v>64.99539</v>
+      </c>
+      <c r="N59">
+        <v>-86.29539</v>
+      </c>
+      <c r="O59">
+        <v>-24.16270919999999</v>
+      </c>
+      <c r="P59">
+        <v>-62.1326808</v>
+      </c>
+      <c r="Q59">
+        <v>-5.032680800000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1723984285592716</v>
+      </c>
+      <c r="T59">
+        <v>2.258927969370438</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.09176035408049708</v>
+      </c>
+      <c r="W59">
+        <v>0.2607123725544227</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.3277155502874896</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2247373766365078</v>
+      </c>
+      <c r="C60">
+        <v>-148.1396436586012</v>
+      </c>
+      <c r="D60">
+        <v>123.8003563413988</v>
+      </c>
+      <c r="E60">
+        <v>136.35</v>
+      </c>
+      <c r="F60">
+        <v>276.95</v>
+      </c>
+      <c r="G60">
+        <v>5.01</v>
+      </c>
+      <c r="H60">
+        <v>336.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>35.8</v>
+      </c>
+      <c r="K60">
+        <v>57.1</v>
+      </c>
+      <c r="L60">
+        <v>-21.3</v>
+      </c>
+      <c r="M60">
+        <v>66.13566</v>
+      </c>
+      <c r="N60">
+        <v>-87.43566000000001</v>
+      </c>
+      <c r="O60">
+        <v>-24.4819848</v>
+      </c>
+      <c r="P60">
+        <v>-62.95367520000002</v>
+      </c>
+      <c r="Q60">
+        <v>-5.853675200000019</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1755793435249685</v>
+      </c>
+      <c r="T60">
+        <v>2.312711968641162</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.09017827901014369</v>
+      </c>
+      <c r="W60">
+        <v>0.2603345730276224</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.3220652821790848</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2267373766365077</v>
+      </c>
+      <c r="C61">
+        <v>-154.2318747047362</v>
+      </c>
+      <c r="D61">
+        <v>122.4831252952638</v>
+      </c>
+      <c r="E61">
+        <v>141.125</v>
+      </c>
+      <c r="F61">
+        <v>281.725</v>
+      </c>
+      <c r="G61">
+        <v>5.01</v>
+      </c>
+      <c r="H61">
+        <v>336.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>35.8</v>
+      </c>
+      <c r="K61">
+        <v>57.1</v>
+      </c>
+      <c r="L61">
+        <v>-21.3</v>
+      </c>
+      <c r="M61">
+        <v>67.27592999999999</v>
+      </c>
+      <c r="N61">
+        <v>-88.57593</v>
+      </c>
+      <c r="O61">
+        <v>-24.80126039999999</v>
+      </c>
+      <c r="P61">
+        <v>-63.77466960000001</v>
+      </c>
+      <c r="Q61">
+        <v>-6.674669600000009</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.178915425074358</v>
+      </c>
+      <c r="T61">
+        <v>2.36911957763241</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.0886498336031921</v>
+      </c>
+      <c r="W61">
+        <v>0.2599695802644423</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.3166065485828291</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2287373766365077</v>
+      </c>
+      <c r="C62">
+        <v>-160.2963702795419</v>
+      </c>
+      <c r="D62">
+        <v>121.1936297204581</v>
+      </c>
+      <c r="E62">
+        <v>145.9</v>
+      </c>
+      <c r="F62">
+        <v>286.5</v>
+      </c>
+      <c r="G62">
+        <v>5.01</v>
+      </c>
+      <c r="H62">
+        <v>336.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>35.8</v>
+      </c>
+      <c r="K62">
+        <v>57.1</v>
+      </c>
+      <c r="L62">
+        <v>-21.3</v>
+      </c>
+      <c r="M62">
+        <v>68.4162</v>
+      </c>
+      <c r="N62">
+        <v>-89.71620000000001</v>
+      </c>
+      <c r="O62">
+        <v>-25.120536</v>
+      </c>
+      <c r="P62">
+        <v>-64.59566400000001</v>
+      </c>
+      <c r="Q62">
+        <v>-7.495664000000012</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.182418310701217</v>
+      </c>
+      <c r="T62">
+        <v>2.42834756707322</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.08717233637647223</v>
+      </c>
+      <c r="W62">
+        <v>0.2596167539267016</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.3113297727731152</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2307373766365078</v>
+      </c>
+      <c r="C63">
+        <v>-166.3339972492271</v>
+      </c>
+      <c r="D63">
+        <v>119.9310027507729</v>
+      </c>
+      <c r="E63">
+        <v>150.675</v>
+      </c>
+      <c r="F63">
+        <v>291.275</v>
+      </c>
+      <c r="G63">
+        <v>5.01</v>
+      </c>
+      <c r="H63">
+        <v>336.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>35.8</v>
+      </c>
+      <c r="K63">
+        <v>57.1</v>
+      </c>
+      <c r="L63">
+        <v>-21.3</v>
+      </c>
+      <c r="M63">
+        <v>69.55647</v>
+      </c>
+      <c r="N63">
+        <v>-90.85647</v>
+      </c>
+      <c r="O63">
+        <v>-25.43981159999999</v>
+      </c>
+      <c r="P63">
+        <v>-65.41665840000002</v>
+      </c>
+      <c r="Q63">
+        <v>-8.316658400000016</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1861008314884277</v>
+      </c>
+      <c r="T63">
+        <v>2.490612889305867</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.08574328168177596</v>
+      </c>
+      <c r="W63">
+        <v>0.2592754956656081</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.3062260060063426</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2327373766365077</v>
+      </c>
+      <c r="C64">
+        <v>-172.3455867275227</v>
+      </c>
+      <c r="D64">
+        <v>118.6944132724772</v>
+      </c>
+      <c r="E64">
+        <v>155.45</v>
+      </c>
+      <c r="F64">
+        <v>296.05</v>
+      </c>
+      <c r="G64">
+        <v>5.01</v>
+      </c>
+      <c r="H64">
+        <v>336.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>35.8</v>
+      </c>
+      <c r="K64">
+        <v>57.1</v>
+      </c>
+      <c r="L64">
+        <v>-21.3</v>
+      </c>
+      <c r="M64">
+        <v>70.69674000000001</v>
+      </c>
+      <c r="N64">
+        <v>-91.99674000000002</v>
+      </c>
+      <c r="O64">
+        <v>-25.7590872</v>
+      </c>
+      <c r="P64">
+        <v>-66.23765280000002</v>
+      </c>
+      <c r="Q64">
+        <v>-9.137652800000019</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1899771691591758</v>
+      </c>
+      <c r="T64">
+        <v>2.556155333761285</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.08436032552561828</v>
+      </c>
+      <c r="W64">
+        <v>0.2589452457355176</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.3012868768772083</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2347373766365078</v>
+      </c>
+      <c r="C65">
+        <v>-178.3319359000618</v>
+      </c>
+      <c r="D65">
+        <v>117.4830640999382</v>
+      </c>
+      <c r="E65">
+        <v>160.225</v>
+      </c>
+      <c r="F65">
+        <v>300.825</v>
+      </c>
+      <c r="G65">
+        <v>5.01</v>
+      </c>
+      <c r="H65">
+        <v>336.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>35.8</v>
+      </c>
+      <c r="K65">
+        <v>57.1</v>
+      </c>
+      <c r="L65">
+        <v>-21.3</v>
+      </c>
+      <c r="M65">
+        <v>71.83701000000001</v>
+      </c>
+      <c r="N65">
+        <v>-93.13701</v>
+      </c>
+      <c r="O65">
+        <v>-26.07836279999999</v>
+      </c>
+      <c r="P65">
+        <v>-67.05864720000001</v>
+      </c>
+      <c r="Q65">
+        <v>-9.958647200000009</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1940630385959102</v>
+      </c>
+      <c r="T65">
+        <v>2.62524061305213</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.08302127273949736</v>
+      </c>
+      <c r="W65">
+        <v>0.258625479930192</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.2965045454982049</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2367373766365077</v>
+      </c>
+      <c r="C66">
+        <v>-184.2938097381733</v>
+      </c>
+      <c r="D66">
+        <v>116.2961902618267</v>
+      </c>
+      <c r="E66">
         <v>165</v>
       </c>
-      <c r="AH3">
-        <v>0.4419256835709278</v>
-      </c>
-      <c r="AI3">
-        <v>0.3192638865439811</v>
-      </c>
-      <c r="AJ3">
-        <v>0.4086181277860327</v>
-      </c>
-      <c r="AK3">
-        <v>0.2903907074973601</v>
-      </c>
-      <c r="AL3">
-        <v>6.99</v>
-      </c>
-      <c r="AM3">
-        <v>6.936</v>
-      </c>
-      <c r="AN3">
-        <v>4.049250535331906</v>
-      </c>
-      <c r="AO3">
-        <v>-1.413447782546495</v>
-      </c>
-      <c r="AP3">
-        <v>3.533190578158458</v>
-      </c>
-      <c r="AQ3">
-        <v>-1.424452133794694</v>
+      <c r="F66">
+        <v>305.6</v>
+      </c>
+      <c r="G66">
+        <v>5.01</v>
+      </c>
+      <c r="H66">
+        <v>336.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>35.8</v>
+      </c>
+      <c r="K66">
+        <v>57.1</v>
+      </c>
+      <c r="L66">
+        <v>-21.3</v>
+      </c>
+      <c r="M66">
+        <v>72.97728000000001</v>
+      </c>
+      <c r="N66">
+        <v>-94.27728000000002</v>
+      </c>
+      <c r="O66">
+        <v>-26.3976384</v>
+      </c>
+      <c r="P66">
+        <v>-67.87964160000001</v>
+      </c>
+      <c r="Q66">
+        <v>-10.77964160000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.19837590077913</v>
+      </c>
+      <c r="T66">
+        <v>2.698163963414689</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.0817240653529427</v>
+      </c>
+      <c r="W66">
+        <v>0.2583157068062827</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.2918716619747956</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2387373766365077</v>
+      </c>
+      <c r="C67">
+        <v>-190.2319426098351</v>
+      </c>
+      <c r="D67">
+        <v>115.1330573901649</v>
+      </c>
+      <c r="E67">
+        <v>169.775</v>
+      </c>
+      <c r="F67">
+        <v>310.375</v>
+      </c>
+      <c r="G67">
+        <v>5.01</v>
+      </c>
+      <c r="H67">
+        <v>336.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>35.8</v>
+      </c>
+      <c r="K67">
+        <v>57.1</v>
+      </c>
+      <c r="L67">
+        <v>-21.3</v>
+      </c>
+      <c r="M67">
+        <v>74.11755000000001</v>
+      </c>
+      <c r="N67">
+        <v>-95.41755000000001</v>
+      </c>
+      <c r="O67">
+        <v>-26.71691399999999</v>
+      </c>
+      <c r="P67">
+        <v>-68.70063600000002</v>
+      </c>
+      <c r="Q67">
+        <v>-11.60063600000002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2029352122299622</v>
+      </c>
+      <c r="T67">
+        <v>2.775254362369395</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.0804667720398205</v>
+      </c>
+      <c r="W67">
+        <v>0.2580154651631091</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.2873813287136446</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2407373766365077</v>
+      </c>
+      <c r="C68">
+        <v>-196.1470397949111</v>
+      </c>
+      <c r="D68">
+        <v>113.992960205089</v>
+      </c>
+      <c r="E68">
+        <v>174.55</v>
+      </c>
+      <c r="F68">
+        <v>315.15</v>
+      </c>
+      <c r="G68">
+        <v>5.01</v>
+      </c>
+      <c r="H68">
+        <v>336.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>35.8</v>
+      </c>
+      <c r="K68">
+        <v>57.1</v>
+      </c>
+      <c r="L68">
+        <v>-21.3</v>
+      </c>
+      <c r="M68">
+        <v>75.25782000000001</v>
+      </c>
+      <c r="N68">
+        <v>-96.55782000000002</v>
+      </c>
+      <c r="O68">
+        <v>-27.0361896</v>
+      </c>
+      <c r="P68">
+        <v>-69.52163040000002</v>
+      </c>
+      <c r="Q68">
+        <v>-12.42163040000002</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.20776271847202</v>
+      </c>
+      <c r="T68">
+        <v>2.856879490674377</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.07924757852406566</v>
+      </c>
+      <c r="W68">
+        <v>0.2577243217515469</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.2830270661573775</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2427373766365078</v>
+      </c>
+      <c r="C69">
+        <v>-202.0397789112452</v>
+      </c>
+      <c r="D69">
+        <v>112.8752210887549</v>
+      </c>
+      <c r="E69">
+        <v>179.325</v>
+      </c>
+      <c r="F69">
+        <v>319.925</v>
+      </c>
+      <c r="G69">
+        <v>5.01</v>
+      </c>
+      <c r="H69">
+        <v>336.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>35.8</v>
+      </c>
+      <c r="K69">
+        <v>57.1</v>
+      </c>
+      <c r="L69">
+        <v>-21.3</v>
+      </c>
+      <c r="M69">
+        <v>76.39809000000001</v>
+      </c>
+      <c r="N69">
+        <v>-97.69809000000001</v>
+      </c>
+      <c r="O69">
+        <v>-27.35546519999999</v>
+      </c>
+      <c r="P69">
+        <v>-70.34262480000001</v>
+      </c>
+      <c r="Q69">
+        <v>-13.24262480000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.21288280084996</v>
+      </c>
+      <c r="T69">
+        <v>2.943451596452389</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.07806477884460199</v>
+      </c>
+      <c r="W69">
+        <v>0.257441869188091</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.2788027815878642</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2447373766365077</v>
+      </c>
+      <c r="C70">
+        <v>-207.910811257669</v>
+      </c>
+      <c r="D70">
+        <v>111.7791887423311</v>
+      </c>
+      <c r="E70">
+        <v>184.1000000000001</v>
+      </c>
+      <c r="F70">
+        <v>324.7</v>
+      </c>
+      <c r="G70">
+        <v>5.01</v>
+      </c>
+      <c r="H70">
+        <v>336.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>35.8</v>
+      </c>
+      <c r="K70">
+        <v>57.1</v>
+      </c>
+      <c r="L70">
+        <v>-21.3</v>
+      </c>
+      <c r="M70">
+        <v>77.53836000000001</v>
+      </c>
+      <c r="N70">
+        <v>-98.83836000000002</v>
+      </c>
+      <c r="O70">
+        <v>-27.6747408</v>
+      </c>
+      <c r="P70">
+        <v>-71.16361920000003</v>
+      </c>
+      <c r="Q70">
+        <v>-14.06361920000003</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2183228883765213</v>
+      </c>
+      <c r="T70">
+        <v>3.035434458841526</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.07691676739100491</v>
+      </c>
+      <c r="W70">
+        <v>0.257167724052972</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.2747027406821605</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2467373766365077</v>
+      </c>
+      <c r="C71">
+        <v>-213.7607630795184</v>
+      </c>
+      <c r="D71">
+        <v>110.7042369204816</v>
+      </c>
+      <c r="E71">
+        <v>188.875</v>
+      </c>
+      <c r="F71">
+        <v>329.475</v>
+      </c>
+      <c r="G71">
+        <v>5.01</v>
+      </c>
+      <c r="H71">
+        <v>336.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>35.8</v>
+      </c>
+      <c r="K71">
+        <v>57.1</v>
+      </c>
+      <c r="L71">
+        <v>-21.3</v>
+      </c>
+      <c r="M71">
+        <v>78.67863000000001</v>
+      </c>
+      <c r="N71">
+        <v>-99.97863000000001</v>
+      </c>
+      <c r="O71">
+        <v>-27.9940164</v>
+      </c>
+      <c r="P71">
+        <v>-71.98461360000002</v>
+      </c>
+      <c r="Q71">
+        <v>-14.88461360000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2241139492918929</v>
+      </c>
+      <c r="T71">
+        <v>3.133351699449317</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.07580203163171496</v>
+      </c>
+      <c r="W71">
+        <v>0.2569015251536536</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.2707215415418391</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2487373766365077</v>
+      </c>
+      <c r="C72">
+        <v>-219.5902367618239</v>
+      </c>
+      <c r="D72">
+        <v>109.6497632381761</v>
+      </c>
+      <c r="E72">
+        <v>193.6500000000001</v>
+      </c>
+      <c r="F72">
+        <v>334.2500000000001</v>
+      </c>
+      <c r="G72">
+        <v>5.01</v>
+      </c>
+      <c r="H72">
+        <v>336.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>35.8</v>
+      </c>
+      <c r="K72">
+        <v>57.1</v>
+      </c>
+      <c r="L72">
+        <v>-21.3</v>
+      </c>
+      <c r="M72">
+        <v>79.81890000000001</v>
+      </c>
+      <c r="N72">
+        <v>-101.1189</v>
+      </c>
+      <c r="O72">
+        <v>-28.313292</v>
+      </c>
+      <c r="P72">
+        <v>-72.80560800000003</v>
+      </c>
+      <c r="Q72">
+        <v>-15.70560800000003</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.230291080934956</v>
+      </c>
+      <c r="T72">
+        <v>3.237796756097628</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.07471914546554762</v>
+      </c>
+      <c r="W72">
+        <v>0.2566429319371728</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.2668540909483845</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2507373766365077</v>
+      </c>
+      <c r="C73">
+        <v>-225.3998119549524</v>
+      </c>
+      <c r="D73">
+        <v>108.6151880450476</v>
+      </c>
+      <c r="E73">
+        <v>198.425</v>
+      </c>
+      <c r="F73">
+        <v>339.025</v>
+      </c>
+      <c r="G73">
+        <v>5.01</v>
+      </c>
+      <c r="H73">
+        <v>336.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>35.8</v>
+      </c>
+      <c r="K73">
+        <v>57.1</v>
+      </c>
+      <c r="L73">
+        <v>-21.3</v>
+      </c>
+      <c r="M73">
+        <v>80.95917</v>
+      </c>
+      <c r="N73">
+        <v>-102.25917</v>
+      </c>
+      <c r="O73">
+        <v>-28.63256759999999</v>
+      </c>
+      <c r="P73">
+        <v>-73.62660240000002</v>
+      </c>
+      <c r="Q73">
+        <v>-16.52660240000002</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.236894221656851</v>
+      </c>
+      <c r="T73">
+        <v>3.349444920100994</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.07366676313504696</v>
+      </c>
+      <c r="W73">
+        <v>0.2563916230366492</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.263095582625168</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2527373766365077</v>
+      </c>
+      <c r="C74">
+        <v>-231.1900466371216</v>
+      </c>
+      <c r="D74">
+        <v>107.5999533628784</v>
+      </c>
+      <c r="E74">
+        <v>203.2</v>
+      </c>
+      <c r="F74">
+        <v>343.8</v>
+      </c>
+      <c r="G74">
+        <v>5.01</v>
+      </c>
+      <c r="H74">
+        <v>336.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>35.8</v>
+      </c>
+      <c r="K74">
+        <v>57.1</v>
+      </c>
+      <c r="L74">
+        <v>-21.3</v>
+      </c>
+      <c r="M74">
+        <v>82.09944</v>
+      </c>
+      <c r="N74">
+        <v>-103.39944</v>
+      </c>
+      <c r="O74">
+        <v>-28.95184319999999</v>
+      </c>
+      <c r="P74">
+        <v>-74.44759680000001</v>
+      </c>
+      <c r="Q74">
+        <v>-17.34759680000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2439690152874528</v>
+      </c>
+      <c r="T74">
+        <v>3.469067952961744</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.07264361364706019</v>
+      </c>
+      <c r="W74">
+        <v>0.256147294938918</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.2594414773109293</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2547373766365078</v>
+      </c>
+      <c r="C75">
+        <v>-236.9614781178756</v>
+      </c>
+      <c r="D75">
+        <v>106.6035218821244</v>
+      </c>
+      <c r="E75">
+        <v>207.975</v>
+      </c>
+      <c r="F75">
+        <v>348.575</v>
+      </c>
+      <c r="G75">
+        <v>5.01</v>
+      </c>
+      <c r="H75">
+        <v>336.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>35.8</v>
+      </c>
+      <c r="K75">
+        <v>57.1</v>
+      </c>
+      <c r="L75">
+        <v>-21.3</v>
+      </c>
+      <c r="M75">
+        <v>83.23971</v>
+      </c>
+      <c r="N75">
+        <v>-104.53971</v>
+      </c>
+      <c r="O75">
+        <v>-29.2711188</v>
+      </c>
+      <c r="P75">
+        <v>-75.26859120000002</v>
+      </c>
+      <c r="Q75">
+        <v>-18.16859120000002</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2515678677055066</v>
+      </c>
+      <c r="T75">
+        <v>3.597551951219585</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.07164849565189498</v>
+      </c>
+      <c r="W75">
+        <v>0.2559096607616725</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.2558874844710537</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2567373766365078</v>
+      </c>
+      <c r="C76">
+        <v>-242.7146239863182</v>
+      </c>
+      <c r="D76">
+        <v>105.6253760136818</v>
+      </c>
+      <c r="E76">
+        <v>212.75</v>
+      </c>
+      <c r="F76">
+        <v>353.35</v>
+      </c>
+      <c r="G76">
+        <v>5.01</v>
+      </c>
+      <c r="H76">
+        <v>336.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>35.8</v>
+      </c>
+      <c r="K76">
+        <v>57.1</v>
+      </c>
+      <c r="L76">
+        <v>-21.3</v>
+      </c>
+      <c r="M76">
+        <v>84.37998</v>
+      </c>
+      <c r="N76">
+        <v>-105.67998</v>
+      </c>
+      <c r="O76">
+        <v>-29.59039439999999</v>
+      </c>
+      <c r="P76">
+        <v>-76.08958560000001</v>
+      </c>
+      <c r="Q76">
+        <v>-18.98958560000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2597512472326415</v>
+      </c>
+      <c r="T76">
+        <v>3.735919333958801</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.07068027273768018</v>
+      </c>
+      <c r="W76">
+        <v>0.2556784491297581</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.2524295454917149</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2587373766365078</v>
+      </c>
+      <c r="C77">
+        <v>-248.4499830076156</v>
+      </c>
+      <c r="D77">
+        <v>104.6650169923844</v>
+      </c>
+      <c r="E77">
+        <v>217.525</v>
+      </c>
+      <c r="F77">
+        <v>358.125</v>
+      </c>
+      <c r="G77">
+        <v>5.01</v>
+      </c>
+      <c r="H77">
+        <v>336.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>35.8</v>
+      </c>
+      <c r="K77">
+        <v>57.1</v>
+      </c>
+      <c r="L77">
+        <v>-21.3</v>
+      </c>
+      <c r="M77">
+        <v>85.52025</v>
+      </c>
+      <c r="N77">
+        <v>-106.82025</v>
+      </c>
+      <c r="O77">
+        <v>-29.90966999999999</v>
+      </c>
+      <c r="P77">
+        <v>-76.91058000000002</v>
+      </c>
+      <c r="Q77">
+        <v>-19.81058000000002</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2685892971219472</v>
+      </c>
+      <c r="T77">
+        <v>3.885356107317153</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.06973786910117778</v>
+      </c>
+      <c r="W77">
+        <v>0.2554534031413613</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.2490638182184923</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2607373766365078</v>
+      </c>
+      <c r="C78">
+        <v>-254.1680359710342</v>
+      </c>
+      <c r="D78">
+        <v>103.7219640289658</v>
+      </c>
+      <c r="E78">
+        <v>222.3</v>
+      </c>
+      <c r="F78">
+        <v>362.9</v>
+      </c>
+      <c r="G78">
+        <v>5.01</v>
+      </c>
+      <c r="H78">
+        <v>336.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>35.8</v>
+      </c>
+      <c r="K78">
+        <v>57.1</v>
+      </c>
+      <c r="L78">
+        <v>-21.3</v>
+      </c>
+      <c r="M78">
+        <v>86.66052000000001</v>
+      </c>
+      <c r="N78">
+        <v>-107.96052</v>
+      </c>
+      <c r="O78">
+        <v>-30.22894559999999</v>
+      </c>
+      <c r="P78">
+        <v>-77.73157440000001</v>
+      </c>
+      <c r="Q78">
+        <v>-20.63157440000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.278163851168695</v>
+      </c>
+      <c r="T78">
+        <v>4.047245945122035</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.06882026556037281</v>
+      </c>
+      <c r="W78">
+        <v>0.2552342794158171</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.2457866627156171</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2627373766365078</v>
+      </c>
+      <c r="C79">
+        <v>-259.8692464925412</v>
+      </c>
+      <c r="D79">
+        <v>102.7957535074588</v>
+      </c>
+      <c r="E79">
+        <v>227.075</v>
+      </c>
+      <c r="F79">
+        <v>367.675</v>
+      </c>
+      <c r="G79">
+        <v>5.01</v>
+      </c>
+      <c r="H79">
+        <v>336.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>35.8</v>
+      </c>
+      <c r="K79">
+        <v>57.1</v>
+      </c>
+      <c r="L79">
+        <v>-21.3</v>
+      </c>
+      <c r="M79">
+        <v>87.80079000000001</v>
+      </c>
+      <c r="N79">
+        <v>-109.10079</v>
+      </c>
+      <c r="O79">
+        <v>-30.5482212</v>
+      </c>
+      <c r="P79">
+        <v>-78.55256880000002</v>
+      </c>
+      <c r="Q79">
+        <v>-21.45256880000002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2885709751325513</v>
+      </c>
+      <c r="T79">
+        <v>4.22321316012734</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.06792649587777057</v>
+      </c>
+      <c r="W79">
+        <v>0.2550208472156116</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.242594628134895</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2647373766365078</v>
+      </c>
+      <c r="C80">
+        <v>-265.5540617747841</v>
+      </c>
+      <c r="D80">
+        <v>101.8859382252159</v>
+      </c>
+      <c r="E80">
+        <v>231.85</v>
+      </c>
+      <c r="F80">
+        <v>372.45</v>
+      </c>
+      <c r="G80">
+        <v>5.01</v>
+      </c>
+      <c r="H80">
+        <v>336.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>35.8</v>
+      </c>
+      <c r="K80">
+        <v>57.1</v>
+      </c>
+      <c r="L80">
+        <v>-21.3</v>
+      </c>
+      <c r="M80">
+        <v>88.94106000000001</v>
+      </c>
+      <c r="N80">
+        <v>-110.24106</v>
+      </c>
+      <c r="O80">
+        <v>-30.86749679999999</v>
+      </c>
+      <c r="P80">
+        <v>-79.37356320000001</v>
+      </c>
+      <c r="Q80">
+        <v>-22.27356320000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.29992420127494</v>
+      </c>
+      <c r="T80">
+        <v>4.415177394678583</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.06705564336651709</v>
+      </c>
+      <c r="W80">
+        <v>0.2548128876359243</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.2394844405947039</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2667373766365077</v>
+      </c>
+      <c r="C81">
+        <v>-271.2229133270661</v>
+      </c>
+      <c r="D81">
+        <v>100.9920866729339</v>
+      </c>
+      <c r="E81">
+        <v>236.625</v>
+      </c>
+      <c r="F81">
+        <v>377.225</v>
+      </c>
+      <c r="G81">
+        <v>5.01</v>
+      </c>
+      <c r="H81">
+        <v>336.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>35.8</v>
+      </c>
+      <c r="K81">
+        <v>57.1</v>
+      </c>
+      <c r="L81">
+        <v>-21.3</v>
+      </c>
+      <c r="M81">
+        <v>90.08133000000001</v>
+      </c>
+      <c r="N81">
+        <v>-111.38133</v>
+      </c>
+      <c r="O81">
+        <v>-31.1867724</v>
+      </c>
+      <c r="P81">
+        <v>-80.19455760000002</v>
+      </c>
+      <c r="Q81">
+        <v>-23.09455760000002</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3123586870499371</v>
+      </c>
+      <c r="T81">
+        <v>4.625423937282325</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.0662068377542827</v>
+      </c>
+      <c r="W81">
+        <v>0.2546101928557227</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.2364529919795813</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2687373766365078</v>
+      </c>
+      <c r="C82">
+        <v>-276.8762176477524</v>
+      </c>
+      <c r="D82">
+        <v>100.1137823522477</v>
+      </c>
+      <c r="E82">
+        <v>241.4</v>
+      </c>
+      <c r="F82">
+        <v>382</v>
+      </c>
+      <c r="G82">
+        <v>5.01</v>
+      </c>
+      <c r="H82">
+        <v>336.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>35.8</v>
+      </c>
+      <c r="K82">
+        <v>57.1</v>
+      </c>
+      <c r="L82">
+        <v>-21.3</v>
+      </c>
+      <c r="M82">
+        <v>91.22160000000001</v>
+      </c>
+      <c r="N82">
+        <v>-112.5216</v>
+      </c>
+      <c r="O82">
+        <v>-31.50604799999999</v>
+      </c>
+      <c r="P82">
+        <v>-81.01555200000001</v>
+      </c>
+      <c r="Q82">
+        <v>-23.91555200000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.326036621402434</v>
+      </c>
+      <c r="T82">
+        <v>4.856695134146442</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.06537925228235417</v>
+      </c>
+      <c r="W82">
+        <v>0.2544125654450262</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.2334973295798364</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2707373766365077</v>
+      </c>
+      <c r="C83">
+        <v>-282.5143768713754</v>
+      </c>
+      <c r="D83">
+        <v>99.2506231286247</v>
+      </c>
+      <c r="E83">
+        <v>246.175</v>
+      </c>
+      <c r="F83">
+        <v>386.775</v>
+      </c>
+      <c r="G83">
+        <v>5.01</v>
+      </c>
+      <c r="H83">
+        <v>336.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>35.8</v>
+      </c>
+      <c r="K83">
+        <v>57.1</v>
+      </c>
+      <c r="L83">
+        <v>-21.3</v>
+      </c>
+      <c r="M83">
+        <v>92.36187000000001</v>
+      </c>
+      <c r="N83">
+        <v>-113.66187</v>
+      </c>
+      <c r="O83">
+        <v>-31.8253236</v>
+      </c>
+      <c r="P83">
+        <v>-81.83654640000003</v>
+      </c>
+      <c r="Q83">
+        <v>-24.73654640000003</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3411543383183516</v>
+      </c>
+      <c r="T83">
+        <v>5.11231066752257</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.06457210101960906</v>
+      </c>
+      <c r="W83">
+        <v>0.2542198177234826</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.2306146464986039</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2727373766365078</v>
+      </c>
+      <c r="C84">
+        <v>-288.1377793825509</v>
+      </c>
+      <c r="D84">
+        <v>98.40222061744912</v>
+      </c>
+      <c r="E84">
+        <v>250.95</v>
+      </c>
+      <c r="F84">
+        <v>391.55</v>
+      </c>
+      <c r="G84">
+        <v>5.01</v>
+      </c>
+      <c r="H84">
+        <v>336.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>35.8</v>
+      </c>
+      <c r="K84">
+        <v>57.1</v>
+      </c>
+      <c r="L84">
+        <v>-21.3</v>
+      </c>
+      <c r="M84">
+        <v>93.50214000000001</v>
+      </c>
+      <c r="N84">
+        <v>-114.80214</v>
+      </c>
+      <c r="O84">
+        <v>-32.14459919999999</v>
+      </c>
+      <c r="P84">
+        <v>-82.65754080000002</v>
+      </c>
+      <c r="Q84">
+        <v>-25.55754080000002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3579518015582601</v>
+      </c>
+      <c r="T84">
+        <v>5.396327926829381</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.06378463637302845</v>
+      </c>
+      <c r="W84">
+        <v>0.2540317711658792</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.227802272760816</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2747373766365078</v>
+      </c>
+      <c r="C85">
+        <v>-293.7468003986746</v>
+      </c>
+      <c r="D85">
+        <v>97.56819960132539</v>
+      </c>
+      <c r="E85">
+        <v>255.7250000000001</v>
+      </c>
+      <c r="F85">
+        <v>396.325</v>
+      </c>
+      <c r="G85">
+        <v>5.01</v>
+      </c>
+      <c r="H85">
+        <v>336.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>35.8</v>
+      </c>
+      <c r="K85">
+        <v>57.1</v>
+      </c>
+      <c r="L85">
+        <v>-21.3</v>
+      </c>
+      <c r="M85">
+        <v>94.64241000000001</v>
+      </c>
+      <c r="N85">
+        <v>-115.94241</v>
+      </c>
+      <c r="O85">
+        <v>-32.4638748</v>
+      </c>
+      <c r="P85">
+        <v>-83.47853520000002</v>
+      </c>
+      <c r="Q85">
+        <v>-26.37853520000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3767254369440401</v>
+      </c>
+      <c r="T85">
+        <v>5.713758981348756</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.06301614677817269</v>
+      </c>
+      <c r="W85">
+        <v>0.2538482558506276</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.2250576670649027</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2767373766365077</v>
+      </c>
+      <c r="C86">
+        <v>-299.3418025232343</v>
+      </c>
+      <c r="D86">
+        <v>96.74819747676567</v>
+      </c>
+      <c r="E86">
+        <v>260.5</v>
+      </c>
+      <c r="F86">
+        <v>401.1</v>
+      </c>
+      <c r="G86">
+        <v>5.01</v>
+      </c>
+      <c r="H86">
+        <v>336.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>35.8</v>
+      </c>
+      <c r="K86">
+        <v>57.1</v>
+      </c>
+      <c r="L86">
+        <v>-21.3</v>
+      </c>
+      <c r="M86">
+        <v>95.78268</v>
+      </c>
+      <c r="N86">
+        <v>-117.08268</v>
+      </c>
+      <c r="O86">
+        <v>-32.78315039999999</v>
+      </c>
+      <c r="P86">
+        <v>-84.29952960000003</v>
+      </c>
+      <c r="Q86">
+        <v>-27.19952960000003</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3978457767530423</v>
+      </c>
+      <c r="T86">
+        <v>6.070868917683049</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.06226595455462303</v>
+      </c>
+      <c r="W86">
+        <v>0.253669109947644</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.2223784091236538</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2787373766365078</v>
+      </c>
+      <c r="C87">
+        <v>-304.9231362714546</v>
+      </c>
+      <c r="D87">
+        <v>95.94186372854544</v>
+      </c>
+      <c r="E87">
+        <v>265.275</v>
+      </c>
+      <c r="F87">
+        <v>405.875</v>
+      </c>
+      <c r="G87">
+        <v>5.01</v>
+      </c>
+      <c r="H87">
+        <v>336.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>35.8</v>
+      </c>
+      <c r="K87">
+        <v>57.1</v>
+      </c>
+      <c r="L87">
+        <v>-21.3</v>
+      </c>
+      <c r="M87">
+        <v>96.92295</v>
+      </c>
+      <c r="N87">
+        <v>-118.22295</v>
+      </c>
+      <c r="O87">
+        <v>-33.10242599999999</v>
+      </c>
+      <c r="P87">
+        <v>-85.12052400000002</v>
+      </c>
+      <c r="Q87">
+        <v>-28.02052400000002</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4217821618699119</v>
+      </c>
+      <c r="T87">
+        <v>6.475593512195253</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.06153341391280392</v>
+      </c>
+      <c r="W87">
+        <v>0.2534941792423776</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.2197621925457283</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2807373766365078</v>
+      </c>
+      <c r="C88">
+        <v>-310.4911405698715</v>
+      </c>
+      <c r="D88">
+        <v>95.14885943012847</v>
+      </c>
+      <c r="E88">
+        <v>270.05</v>
+      </c>
+      <c r="F88">
+        <v>410.65</v>
+      </c>
+      <c r="G88">
+        <v>5.01</v>
+      </c>
+      <c r="H88">
+        <v>336.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>35.8</v>
+      </c>
+      <c r="K88">
+        <v>57.1</v>
+      </c>
+      <c r="L88">
+        <v>-21.3</v>
+      </c>
+      <c r="M88">
+        <v>98.06322</v>
+      </c>
+      <c r="N88">
+        <v>-119.36322</v>
+      </c>
+      <c r="O88">
+        <v>-33.42170159999999</v>
+      </c>
+      <c r="P88">
+        <v>-85.94151840000002</v>
+      </c>
+      <c r="Q88">
+        <v>-28.84151840000002</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4491380305749056</v>
+      </c>
+      <c r="T88">
+        <v>6.938135905923487</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.06081790909986435</v>
+      </c>
+      <c r="W88">
+        <v>0.2533233166930476</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.2172068182138014</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2827373766365078</v>
+      </c>
+      <c r="C89">
+        <v>-316.0461432313373</v>
+      </c>
+      <c r="D89">
+        <v>94.36885676866272</v>
+      </c>
+      <c r="E89">
+        <v>274.825</v>
+      </c>
+      <c r="F89">
+        <v>415.425</v>
+      </c>
+      <c r="G89">
+        <v>5.01</v>
+      </c>
+      <c r="H89">
+        <v>336.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>35.8</v>
+      </c>
+      <c r="K89">
+        <v>57.1</v>
+      </c>
+      <c r="L89">
+        <v>-21.3</v>
+      </c>
+      <c r="M89">
+        <v>99.20349</v>
+      </c>
+      <c r="N89">
+        <v>-120.50349</v>
+      </c>
+      <c r="O89">
+        <v>-33.74097719999999</v>
+      </c>
+      <c r="P89">
+        <v>-86.76251280000001</v>
+      </c>
+      <c r="Q89">
+        <v>-29.66251280000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.480702494465283</v>
+      </c>
+      <c r="T89">
+        <v>7.4718386679176</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.06011885267342913</v>
+      </c>
+      <c r="W89">
+        <v>0.2531563820184149</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.2147101881193898</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2847373766365077</v>
+      </c>
+      <c r="C90">
+        <v>-321.5884614068489</v>
+      </c>
+      <c r="D90">
+        <v>93.6015385931511</v>
+      </c>
+      <c r="E90">
+        <v>279.6</v>
+      </c>
+      <c r="F90">
+        <v>420.2</v>
+      </c>
+      <c r="G90">
+        <v>5.01</v>
+      </c>
+      <c r="H90">
+        <v>336.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>35.8</v>
+      </c>
+      <c r="K90">
+        <v>57.1</v>
+      </c>
+      <c r="L90">
+        <v>-21.3</v>
+      </c>
+      <c r="M90">
+        <v>100.34376</v>
+      </c>
+      <c r="N90">
+        <v>-121.64376</v>
+      </c>
+      <c r="O90">
+        <v>-34.06025279999999</v>
+      </c>
+      <c r="P90">
+        <v>-87.58350720000001</v>
+      </c>
+      <c r="Q90">
+        <v>-30.48350720000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5175277023373899</v>
+      </c>
+      <c r="T90">
+        <v>8.094491890244068</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.05943568389304925</v>
+      </c>
+      <c r="W90">
+        <v>0.2529932413136602</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.2122702996180332</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2867373766365077</v>
+      </c>
+      <c r="C91">
+        <v>-327.1184020155136</v>
+      </c>
+      <c r="D91">
+        <v>92.84659798448644</v>
+      </c>
+      <c r="E91">
+        <v>284.375</v>
+      </c>
+      <c r="F91">
+        <v>424.975</v>
+      </c>
+      <c r="G91">
+        <v>5.01</v>
+      </c>
+      <c r="H91">
+        <v>336.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>35.8</v>
+      </c>
+      <c r="K91">
+        <v>57.1</v>
+      </c>
+      <c r="L91">
+        <v>-21.3</v>
+      </c>
+      <c r="M91">
+        <v>101.48403</v>
+      </c>
+      <c r="N91">
+        <v>-122.78403</v>
+      </c>
+      <c r="O91">
+        <v>-34.37952839999999</v>
+      </c>
+      <c r="P91">
+        <v>-88.4045016</v>
+      </c>
+      <c r="Q91">
+        <v>-31.3045016</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5610484025498799</v>
+      </c>
+      <c r="T91">
+        <v>8.830354789357166</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.05876786722009363</v>
+      </c>
+      <c r="W91">
+        <v>0.2528337666921583</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.209885240071763</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2887373766365077</v>
+      </c>
+      <c r="C92">
+        <v>-332.6362621538718</v>
+      </c>
+      <c r="D92">
+        <v>92.10373784612823</v>
+      </c>
+      <c r="E92">
+        <v>289.15</v>
+      </c>
+      <c r="F92">
+        <v>429.75</v>
+      </c>
+      <c r="G92">
+        <v>5.01</v>
+      </c>
+      <c r="H92">
+        <v>336.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>35.8</v>
+      </c>
+      <c r="K92">
+        <v>57.1</v>
+      </c>
+      <c r="L92">
+        <v>-21.3</v>
+      </c>
+      <c r="M92">
+        <v>102.6243</v>
+      </c>
+      <c r="N92">
+        <v>-123.9243</v>
+      </c>
+      <c r="O92">
+        <v>-34.698804</v>
+      </c>
+      <c r="P92">
+        <v>-89.22549600000002</v>
+      </c>
+      <c r="Q92">
+        <v>-32.12549600000002</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6132732428048679</v>
+      </c>
+      <c r="T92">
+        <v>9.713390268292883</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.05811489091764815</v>
+      </c>
+      <c r="W92">
+        <v>0.2526778359511344</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.2075531818487435</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2907373766365077</v>
+      </c>
+      <c r="C93">
+        <v>-338.1423294857273</v>
+      </c>
+      <c r="D93">
+        <v>91.3726705142727</v>
+      </c>
+      <c r="E93">
+        <v>293.9250000000001</v>
+      </c>
+      <c r="F93">
+        <v>434.525</v>
+      </c>
+      <c r="G93">
+        <v>5.01</v>
+      </c>
+      <c r="H93">
+        <v>336.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>35.8</v>
+      </c>
+      <c r="K93">
+        <v>57.1</v>
+      </c>
+      <c r="L93">
+        <v>-21.3</v>
+      </c>
+      <c r="M93">
+        <v>103.76457</v>
+      </c>
+      <c r="N93">
+        <v>-125.06457</v>
+      </c>
+      <c r="O93">
+        <v>-35.0180796</v>
+      </c>
+      <c r="P93">
+        <v>-90.04649040000004</v>
+      </c>
+      <c r="Q93">
+        <v>-32.94649040000004</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6771036031165201</v>
+      </c>
+      <c r="T93">
+        <v>10.79265585365876</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.05747626574272893</v>
+      </c>
+      <c r="W93">
+        <v>0.2525253322593637</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.2052723776526035</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2927373766365078</v>
+      </c>
+      <c r="C94">
+        <v>-343.6368826135583</v>
+      </c>
+      <c r="D94">
+        <v>90.65311738644175</v>
+      </c>
+      <c r="E94">
+        <v>298.7</v>
+      </c>
+      <c r="F94">
+        <v>439.3</v>
+      </c>
+      <c r="G94">
+        <v>5.01</v>
+      </c>
+      <c r="H94">
+        <v>336.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>35.8</v>
+      </c>
+      <c r="K94">
+        <v>57.1</v>
+      </c>
+      <c r="L94">
+        <v>-21.3</v>
+      </c>
+      <c r="M94">
+        <v>104.90484</v>
+      </c>
+      <c r="N94">
+        <v>-126.20484</v>
+      </c>
+      <c r="O94">
+        <v>-35.3373552</v>
+      </c>
+      <c r="P94">
+        <v>-90.86748480000003</v>
+      </c>
+      <c r="Q94">
+        <v>-33.76748480000003</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7568915535060854</v>
+      </c>
+      <c r="T94">
+        <v>12.14173783536611</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.05685152372378623</v>
+      </c>
+      <c r="W94">
+        <v>0.2523761438652402</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.2030411561563796</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2947373766365077</v>
+      </c>
+      <c r="C95">
+        <v>-349.120191432515</v>
+      </c>
+      <c r="D95">
+        <v>89.94480856748507</v>
+      </c>
+      <c r="E95">
+        <v>303.475</v>
+      </c>
+      <c r="F95">
+        <v>444.075</v>
+      </c>
+      <c r="G95">
+        <v>5.01</v>
+      </c>
+      <c r="H95">
+        <v>336.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>35.8</v>
+      </c>
+      <c r="K95">
+        <v>57.1</v>
+      </c>
+      <c r="L95">
+        <v>-21.3</v>
+      </c>
+      <c r="M95">
+        <v>106.04511</v>
+      </c>
+      <c r="N95">
+        <v>-127.34511</v>
+      </c>
+      <c r="O95">
+        <v>-35.6566308</v>
+      </c>
+      <c r="P95">
+        <v>-91.68847920000003</v>
+      </c>
+      <c r="Q95">
+        <v>-34.58847920000003</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8594760611498118</v>
+      </c>
+      <c r="T95">
+        <v>13.87627181184698</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.05624021701707884</v>
+      </c>
+      <c r="W95">
+        <v>0.2522301638236784</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.2008579179181389</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2967373766365077</v>
+      </c>
+      <c r="C96">
+        <v>-354.5925174679525</v>
+      </c>
+      <c r="D96">
+        <v>89.24748253204758</v>
+      </c>
+      <c r="E96">
+        <v>308.25</v>
+      </c>
+      <c r="F96">
+        <v>448.85</v>
+      </c>
+      <c r="G96">
+        <v>5.01</v>
+      </c>
+      <c r="H96">
+        <v>336.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>35.8</v>
+      </c>
+      <c r="K96">
+        <v>57.1</v>
+      </c>
+      <c r="L96">
+        <v>-21.3</v>
+      </c>
+      <c r="M96">
+        <v>107.18538</v>
+      </c>
+      <c r="N96">
+        <v>-128.48538</v>
+      </c>
+      <c r="O96">
+        <v>-35.97590639999999</v>
+      </c>
+      <c r="P96">
+        <v>-92.50947360000004</v>
+      </c>
+      <c r="Q96">
+        <v>-35.40947360000003</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9962554046747807</v>
+      </c>
+      <c r="T96">
+        <v>16.18898378048815</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.0556419168360461</v>
+      </c>
+      <c r="W96">
+        <v>0.2520872897404478</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.1987211315573076</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2987373766365078</v>
+      </c>
+      <c r="C97">
+        <v>-360.0541141973817</v>
+      </c>
+      <c r="D97">
+        <v>88.56088580261837</v>
+      </c>
+      <c r="E97">
+        <v>313.0250000000001</v>
+      </c>
+      <c r="F97">
+        <v>453.6250000000001</v>
+      </c>
+      <c r="G97">
+        <v>5.01</v>
+      </c>
+      <c r="H97">
+        <v>336.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>35.8</v>
+      </c>
+      <c r="K97">
+        <v>57.1</v>
+      </c>
+      <c r="L97">
+        <v>-21.3</v>
+      </c>
+      <c r="M97">
+        <v>108.32565</v>
+      </c>
+      <c r="N97">
+        <v>-129.62565</v>
+      </c>
+      <c r="O97">
+        <v>-36.295182</v>
+      </c>
+      <c r="P97">
+        <v>-93.33046800000004</v>
+      </c>
+      <c r="Q97">
+        <v>-36.23046800000004</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.187746485609738</v>
+      </c>
+      <c r="T97">
+        <v>19.4267805365858</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.05505621244829824</v>
+      </c>
+      <c r="W97">
+        <v>0.2519474235326536</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.1966293301724937</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3007373766365077</v>
+      </c>
+      <c r="C98">
+        <v>-365.5052273576736</v>
+      </c>
+      <c r="D98">
+        <v>87.88477264232635</v>
+      </c>
+      <c r="E98">
+        <v>317.8</v>
+      </c>
+      <c r="F98">
+        <v>458.4</v>
+      </c>
+      <c r="G98">
+        <v>5.01</v>
+      </c>
+      <c r="H98">
+        <v>336.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>35.8</v>
+      </c>
+      <c r="K98">
+        <v>57.1</v>
+      </c>
+      <c r="L98">
+        <v>-21.3</v>
+      </c>
+      <c r="M98">
+        <v>109.46592</v>
+      </c>
+      <c r="N98">
+        <v>-130.76592</v>
+      </c>
+      <c r="O98">
+        <v>-36.61445759999999</v>
+      </c>
+      <c r="P98">
+        <v>-94.15146240000001</v>
+      </c>
+      <c r="Q98">
+        <v>-37.05146240000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.474983107012169</v>
+      </c>
+      <c r="T98">
+        <v>24.28347567073219</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.05448271023529514</v>
+      </c>
+      <c r="W98">
+        <v>0.2518104712041885</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.1945811079831969</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3027373766365077</v>
+      </c>
+      <c r="C99">
+        <v>-370.9460952382984</v>
+      </c>
+      <c r="D99">
+        <v>87.21890476170161</v>
+      </c>
+      <c r="E99">
+        <v>322.575</v>
+      </c>
+      <c r="F99">
+        <v>463.175</v>
+      </c>
+      <c r="G99">
+        <v>5.01</v>
+      </c>
+      <c r="H99">
+        <v>336.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>35.8</v>
+      </c>
+      <c r="K99">
+        <v>57.1</v>
+      </c>
+      <c r="L99">
+        <v>-21.3</v>
+      </c>
+      <c r="M99">
+        <v>110.60619</v>
+      </c>
+      <c r="N99">
+        <v>-131.90619</v>
+      </c>
+      <c r="O99">
+        <v>-36.93373319999999</v>
+      </c>
+      <c r="P99">
+        <v>-94.97245680000002</v>
+      </c>
+      <c r="Q99">
+        <v>-37.87245680000002</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.953710809349558</v>
+      </c>
+      <c r="T99">
+        <v>32.37796756097624</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.053921032810189</v>
+      </c>
+      <c r="W99">
+        <v>0.2516763426350731</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.1925751171792465</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3047373766365077</v>
+      </c>
+      <c r="C100">
+        <v>-376.3769489613331</v>
+      </c>
+      <c r="D100">
+        <v>86.56305103866686</v>
+      </c>
+      <c r="E100">
+        <v>327.35</v>
+      </c>
+      <c r="F100">
+        <v>467.95</v>
+      </c>
+      <c r="G100">
+        <v>5.01</v>
+      </c>
+      <c r="H100">
+        <v>336.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>35.8</v>
+      </c>
+      <c r="K100">
+        <v>57.1</v>
+      </c>
+      <c r="L100">
+        <v>-21.3</v>
+      </c>
+      <c r="M100">
+        <v>111.74646</v>
+      </c>
+      <c r="N100">
+        <v>-133.04646</v>
+      </c>
+      <c r="O100">
+        <v>-37.25300879999999</v>
+      </c>
+      <c r="P100">
+        <v>-95.79345120000001</v>
+      </c>
+      <c r="Q100">
+        <v>-38.69345120000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.911166214024337</v>
+      </c>
+      <c r="T100">
+        <v>48.56695134146437</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.05337081818967688</v>
+      </c>
+      <c r="W100">
+        <v>0.2515449513836948</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.1906100649631317</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3067373766365077</v>
+      </c>
+      <c r="C101">
+        <v>-381.7980127489317</v>
+      </c>
+      <c r="D101">
+        <v>85.91698725106829</v>
+      </c>
+      <c r="E101">
+        <v>332.125</v>
+      </c>
+      <c r="F101">
+        <v>472.725</v>
+      </c>
+      <c r="G101">
+        <v>5.01</v>
+      </c>
+      <c r="H101">
+        <v>336.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>35.8</v>
+      </c>
+      <c r="K101">
+        <v>57.1</v>
+      </c>
+      <c r="L101">
+        <v>-21.3</v>
+      </c>
+      <c r="M101">
+        <v>112.88673</v>
+      </c>
+      <c r="N101">
+        <v>-134.18673</v>
+      </c>
+      <c r="O101">
+        <v>-37.57228439999999</v>
+      </c>
+      <c r="P101">
+        <v>-96.61444560000001</v>
+      </c>
+      <c r="Q101">
+        <v>-39.51444560000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.783532428048674</v>
+      </c>
+      <c r="T101">
+        <v>97.13390268292873</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.05283171901604377</v>
+      </c>
+      <c r="W101">
+        <v>0.2514162145010312</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.1886847107715848</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
